--- a/naver-place-crawler/results_nail/일산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/일산_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>오니뷰티 네일&amp;속눈썹</t>
+          <t>네일오티디</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>onibeauty@naver.com</t>
+          <t>swc1439@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1486-0275</t>
+          <t>0507-1429-0763</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1036 고양터미널 2층</t>
+          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onibeauty_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4bs31</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1027</v>
+        <v>151</v>
       </c>
       <c r="Q2" t="n">
-        <v>418</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>1445</v>
+        <v>159</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1717534756</t>
+          <t>2026395486</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717534756</t>
+          <t>https://m.place.naver.com/place/2026395486</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일앤스타일</t>
+          <t>라플라마</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nailnstyle_@naver.com</t>
+          <t>kimtso321@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1438-5770</t>
+          <t>0507-1376-0171</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
+          <t>경기도 고양시 일산동구 태극로 8 상가동119호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nstyle_lab</t>
+          <t>https://www.instagram.com/laflamma_</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wchypl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3029</v>
+        <v>693</v>
       </c>
       <c r="Q3" t="n">
-        <v>829</v>
+        <v>142</v>
       </c>
       <c r="R3" t="n">
-        <v>3858</v>
+        <v>835</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>31424432</t>
+          <t>1296944106</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31424432</t>
+          <t>https://m.place.naver.com/place/1296944106</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>이제이네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>diane09@naver.com</t>
+          <t>dmsgml4848@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1463-2316</t>
+          <t>0507-1357-0503</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 강석로 33 상가동 105호</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>http://www.instagram.com/eeej_nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,17 +794,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sr0p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>546</v>
+        <v>326</v>
       </c>
       <c r="Q4" t="n">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
-        <v>681</v>
+        <v>356</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1105591278</t>
+          <t>37902943</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105591278</t>
+          <t>https://m.place.naver.com/place/37902943</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>포쉬네일 뉴코아아울렛일산점</t>
+          <t>주디네일 정발산본점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sg94media@naver.com</t>
+          <t>rkflrkfl1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1486-0212</t>
+          <t>0507-1464-0970</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
+          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_madu</t>
+          <t>https://blog.naver.com/rkflrkfl1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc5wxc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="Q5" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="R5" t="n">
-        <v>595</v>
+        <v>465</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1089108291</t>
+          <t>1885034449</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089108291</t>
+          <t>https://m.place.naver.com/place/1885034449</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일브랜디 일산킨텍스점</t>
+          <t>S뷰티네일 일산주엽점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>romanzhee@naver.com</t>
+          <t>s-beauty06@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1325-6774</t>
+          <t>0507-1327-9513</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_b_randy</t>
+          <t>https://blog.naver.com/s-beauty06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,19 +977,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ua3u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>257</v>
+        <v>478</v>
       </c>
       <c r="Q6" t="n">
-        <v>62</v>
+        <v>426</v>
       </c>
       <c r="R6" t="n">
-        <v>319</v>
+        <v>904</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1125128328</t>
+          <t>1247940545</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125128328</t>
+          <t>https://m.place.naver.com/place/1247940545</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
+          <t>네일스튜디오하몽</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>garinh_56@naver.com</t>
+          <t>laviedekey@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-815-3435</t>
+          <t>0507-1480-0355</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/salondeluce_</t>
+          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1096,17 +1076,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4hi9a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>427</v>
+        <v>585</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>515</v>
+        <v>609</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1385267282</t>
+          <t>1865813904</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1385267282</t>
+          <t>https://m.place.naver.com/place/1865813904</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일갤러리앤속눈썹 야당점</t>
+          <t>포쉬네일 뉴코아아울렛일산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tmsla_zz@naver.com</t>
+          <t>p_yoojin@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1334-0865</t>
+          <t>0507-1486-0212</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1114 206호 네일갤러리</t>
+          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgallery_yd</t>
+          <t>https://www.instagram.com/forsynail_madu</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1033</v>
+        <v>485</v>
       </c>
       <c r="Q8" t="n">
-        <v>393</v>
+        <v>122</v>
       </c>
       <c r="R8" t="n">
-        <v>1426</v>
+        <v>607</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1854020265</t>
+          <t>1089108291</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1854020265</t>
+          <t>https://m.place.naver.com/place/1089108291</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>체리누아</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>herseada@naver.com</t>
+          <t>ksy3315@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1327-2939</t>
+          <t>0507-1385-4858</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 파주시 소리천로 25 214호</t>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cherry_noir_nail_/</t>
+          <t>https://www.instagram.com/nail_ree_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1303,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2091202986</t>
+          <t>1653728375</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091202986</t>
+          <t>https://m.place.naver.com/place/1653728375</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일오티디</t>
+          <t>라망네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>smallsmall0@naver.com</t>
+          <t>ehyeon4862@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1429-0763</t>
+          <t>0507-1409-8266</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
+          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/lamain_naily</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1382,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wj6z8v0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="Q10" t="n">
         <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026395486</t>
+          <t>1819287959</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026395486</t>
+          <t>https://m.place.naver.com/place/1819287959</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1438,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헤넬뷰티네일</t>
+          <t>발톱닥터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>henellbeauty@naver.com</t>
+          <t>jallana@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1403-3243</t>
+          <t>0507-1409-8838</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 78 202호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/henellbeauty_nail</t>
+          <t>https://www.instagram.com/bt_doctor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1475,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1495,32 +1467,6134 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>324</v>
       </c>
       <c r="R11" t="n">
+        <v>479</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>36651631</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36651631</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>다다네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>tykd2048@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1418-7723</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dada._.nail/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22</v>
+      </c>
+      <c r="R12" t="n">
+        <v>103</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1226786349</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1226786349</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>영네일</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>youngnail0121@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1411-7300</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/youngnail0121</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>786</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1073</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13464862</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13464862</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>홀리네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ko3hi@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1353-4205</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/holy._.nail</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>433</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>37849636</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37849636</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>물들다, 네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>norajo89@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1472-1621</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>111</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2066663730</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066663730</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>르네상스</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>suny6668@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>support@herren.co.kr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1406-4890</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/166708</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>511</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>249</v>
+      </c>
+      <c r="R16" t="n">
+        <v>760</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>468197702</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/468197702</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>마이유네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>tasha81@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/my_u_nail</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>63</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2037646051</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037646051</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>라미살롱</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>marsfive@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1386-1988</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rami_salon88</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>701</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>61</v>
+      </c>
+      <c r="R18" t="n">
+        <v>762</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1314158350</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314158350</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>엄네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>molly32@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1333-3487</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 39 대양빌딩 6층 602호 베이뷰티 엄네일</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/umnail.__</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>603</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1924027006</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1924027006</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>어썸네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>loves0226@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_zCyUG/friend</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>30</v>
+      </c>
+      <c r="R20" t="n">
+        <v>98</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1080419201</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1080419201</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>제제샵</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>rowjddms2@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1395-0132</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/all.beauty_jeje</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>367</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>451</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1262615516</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1262615516</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>바이마이네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jjeong_1004_@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1303-0274</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bymynail_</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>196</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1712300996</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1712300996</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>토리네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>torinail9994@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/torinail9994</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>179</v>
+      </c>
+      <c r="R23" t="n">
+        <v>203</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1327373273</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1327373273</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>garinh_56@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>031-815-3435</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://instagram.com/salondeluce_</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>515</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1385267282</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1385267282</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>원네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ohnyoou@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1395-3817</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 탄현로 144-27 2층 202호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/one_nail21</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>86</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2040723368</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2040723368</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>네일피다</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>apple0879@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1495-6782</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 산두로 157 네일피다</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_hSTxeG</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>298</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1164237548</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164237548</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>뮤트뷰티</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mute_e@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1410-0371</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mute_e</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>233</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1641314586</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1641314586</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>네일앤스타일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>nailnstyle_@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1438-5770</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nstyle_lab</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>3037</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>830</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3867</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>31424432</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31424432</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>무이네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>baeyou0417@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1351-6051</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muinail_</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>221</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1218582286</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1218582286</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>네일 바이 무제</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>onesun012@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1330-5463</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nails_by_mooze</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>72</v>
+      </c>
+      <c r="R30" t="n">
         <v>127</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2009159866</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2009159866</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1593406269</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593406269</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>네일_하니</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lunefronde@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1490-1526</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xnDQmn/chat</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>71</v>
+      </c>
+      <c r="R31" t="n">
+        <v>272</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2076477973</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2076477973</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>리아네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ryddltptkd1401@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1356-7914</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 하이파크로 113 아이파크 1단지 상가동 201호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/TYe5QWRPu</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>72</v>
+      </c>
+      <c r="R32" t="n">
+        <v>235</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1188570648</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188570648</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>네일 드 제니</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hja1213@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1416-4932</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_de_jeny</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>147</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1635177150</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1635177150</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>네일누와</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>astro_sexy@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1355-6322</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ClIdn/chat</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23</v>
+      </c>
+      <c r="R34" t="n">
+        <v>190</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1005319723</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1005319723</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>네일스콘</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>alizee8@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1384-0383</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_sTlxmG</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>78</v>
+      </c>
+      <c r="R35" t="n">
+        <v>364</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1345185463</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1345185463</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>네일리쉬</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>moonnsleep@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1384-3764</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_CRNHxd</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>30</v>
+      </c>
+      <c r="R36" t="n">
+        <v>272</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1946279327</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1946279327</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아토네일스튜디오 일산</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sesehhh@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1461-2141</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>924</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>541</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1465</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1419778439</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1419778439</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>츠키네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>minvl@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1328-9708</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thuki_nail/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>345</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1363998342</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1363998342</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>봄꽃네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>molly32@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1350-7728</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 대화2로 137 상가건물 2층 209호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>59</v>
+      </c>
+      <c r="R39" t="n">
+        <v>443</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1461994183</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1461994183</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>네일로희</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>younglia_@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1349-2502</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xlXLKn</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>58</v>
+      </c>
+      <c r="R40" t="n">
+        <v>312</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1049597572</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1049597572</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>네일디어원</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>eee2sia@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1417-4781</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xlCxgxbG</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>890</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>71</v>
+      </c>
+      <c r="R41" t="n">
+        <v>961</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1054380281</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054380281</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>허앤밀네일 일산본점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1387-0713</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heo_mil_nail</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1104</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1110</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1482502953</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1482502953</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>기린네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ssso131@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1468-7932</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kirrin_nail</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>55</v>
+      </c>
+      <c r="R43" t="n">
+        <v>170</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1349667462</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349667462</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>네일르엘</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>apoco123@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1371-6033</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xaLFXG/chat</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>51</v>
+      </c>
+      <c r="R44" t="n">
+        <v>355</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1006093671</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006093671</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>쏘야네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dlthdus1541@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1377-6460</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlthdus1541</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>219</v>
+      </c>
+      <c r="R45" t="n">
+        <v>661</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1952042243</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1952042243</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jujunail0713@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1404-4143</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pediheal_ilsan</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>275</v>
+      </c>
+      <c r="R46" t="n">
+        <v>485</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>13092675</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13092675</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>레몬네일 풍동점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>n-young-@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1311-3135</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을1로 29-37 서광미르프라자 102호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/lemonshop_diary</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>592</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>596</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1457328873</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457328873</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>모던네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>modern_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1381-4140</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 1층 136호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mdna_il</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>77</v>
+      </c>
+      <c r="R48" t="n">
+        <v>313</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1882656587</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1882656587</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>운디아네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>undia10@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1327-8629</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/undia_nail</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1822</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>166</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1988</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1192977296</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192977296</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>네일팩토리</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nailfactory13@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1323-3381</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https:///linktr.ee/Nail_Factory13</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1022</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1032</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1383137709</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1383137709</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>레푸스 일산장항점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>yoonaejang@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1395-4179</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1922</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>645</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2567</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>90030989</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/90030989</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일맑음래쉬</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>rlazzzzzz@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1356-7749</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>9</v>
+      </c>
+      <c r="R52" t="n">
+        <v>46</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1604742986</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604742986</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>소울메이트네일샵</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>algmlspdlf@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1382-5531</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/soulmatenail</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>163</v>
+      </c>
+      <c r="R53" t="n">
+        <v>392</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>36620432</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36620432</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>오니뷰티 네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>onibeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1486-0275</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_onibeauty_/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1030</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>436</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1466</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1717534756</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1717534756</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>오드네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>seong30526@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1368-7567</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Kfxacn</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>16</v>
+      </c>
+      <c r="R55" t="n">
+        <v>79</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026543533</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2026543533</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>제이윤네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>x7129x@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1356-0390</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1160 4층 411호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/j_yun__nail?igsh=NDZwZ2wwOWFkZWZm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>195</v>
+      </c>
+      <c r="R56" t="n">
+        <v>504</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1373645197</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1373645197</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>포쉬네일 홈플러스킨텍스점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lucyjuni@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1333-4281</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/forsynail_kintex</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>463</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>69</v>
+      </c>
+      <c r="R57" t="n">
+        <v>532</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1485591782</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1485591782</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>온네일</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>guswnwnwn@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1347-5700</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onnail__</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1752</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>17</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1769</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>31298365</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31298365</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>제이 뷰티 클리어</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jonghyun0823@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1342-8831</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sBf6NdCd</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>354</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>40</v>
+      </c>
+      <c r="R59" t="n">
+        <v>394</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1701276497</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1701276497</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>디엘 네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>soms0m@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1392-5930</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>64</v>
+      </c>
+      <c r="R60" t="n">
+        <v>151</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2001645591</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001645591</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>네일브랜디 일산킨텍스점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ssso131@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1325-6774</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_b_randy</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>261</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>63</v>
+      </c>
+      <c r="R61" t="n">
+        <v>324</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1125128328</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125128328</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일뮤토</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ithgml123@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1370-0857</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>15</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1260058171</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260058171</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>네일,숩</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>hyunjju1541@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1325-8243</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail___soop</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>5</v>
+      </c>
+      <c r="R63" t="n">
+        <v>150</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1126898433</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1126898433</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>비온네일 일산킨텍스점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>feb_7th@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1384-4180</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_HDxnPn</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>36</v>
+      </c>
+      <c r="R64" t="n">
+        <v>114</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1988141515</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1988141515</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>오묘네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>skme12@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1351-1060</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/5.myo_art</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>29</v>
+      </c>
+      <c r="R65" t="n">
+        <v>311</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1036508811</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036508811</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>조조네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>yhkim5616lmy@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1307-3090</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jojonail.official</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>16</v>
+      </c>
+      <c r="R66" t="n">
+        <v>62</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1911173276</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1911173276</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>더블앤뷰티 레푸스 일산주엽점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>x7x7x7love@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1337-3327</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>389</v>
+      </c>
+      <c r="R67" t="n">
+        <v>812</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1209456950</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1209456950</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>그리심네일&amp;뷰티</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>herb2592@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1329-7483</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/herb2592</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>90</v>
+      </c>
+      <c r="R68" t="n">
+        <v>350</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1667004401</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667004401</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>칙스네일 일산백석점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>chixs_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1324-6973</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chixsnail_</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1174</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>66</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1240</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1834147957</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1834147957</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일더무드</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2skgus7@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1417-7531</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_bWPiG</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>5</v>
+      </c>
+      <c r="R70" t="n">
+        <v>348</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1154624160</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1154624160</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일무아</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>loowowool@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1322-4700</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_mua_</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>79</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2028306533</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2028306533</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>도도네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>mimisuji52@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1416-6295</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 고양대로 685</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mimisuji52</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>14</v>
+      </c>
+      <c r="R72" t="n">
+        <v>112</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1952745044</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1952745044</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>네일은뷰티</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>topnailjina@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1393-0807</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_eunbeauty</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>104</v>
+      </c>
+      <c r="R73" t="n">
+        <v>547</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1421368108</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421368108</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>라온네일</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1463-2316</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>551</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>137</v>
+      </c>
+      <c r="R74" t="n">
+        <v>688</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1105591278</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105591278</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>우네뜨 네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>kimsuji0061@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1387-1893</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1437 화성프라자 5층 503호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woonette._/profilecard/?igsh=MWNyY29tejFuaXViMA==</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>29</v>
+      </c>
+      <c r="R75" t="n">
+        <v>78</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2054238571</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2054238571</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>네일바이아르</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>nailbyare@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1441-7961</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbyare/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>66</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2094840936</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2094840936</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/일산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/일산_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일오티디</t>
+          <t>허앤밀네일 일산본점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>swc1439@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1429-0763</t>
+          <t>0507-1387-0713</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
+          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heo_mil_nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>151</v>
+        <v>1106</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>159</v>
+        <v>1112</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026395486</t>
+          <t>1482502953</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026395486</t>
+          <t>https://m.place.naver.com/place/1482502953</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>라플라마</t>
+          <t>네일로희</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kimtso321@naver.com</t>
+          <t>younglia_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1376-0171</t>
+          <t>0507-1349-2502</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 태극로 8 상가동119호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laflamma_</t>
+          <t>http://pf.kakao.com/_xlXLKn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>693</v>
+        <v>255</v>
       </c>
       <c r="Q3" t="n">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="R3" t="n">
-        <v>835</v>
+        <v>312</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1296944106</t>
+          <t>1049597572</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296944106</t>
+          <t>https://m.place.naver.com/place/1049597572</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이제이네일</t>
+          <t>S뷰티네일 일산주엽점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dmsgml4848@naver.com</t>
+          <t>s-beauty06@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1357-0503</t>
+          <t>0507-1327-9513</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/eeej_nail</t>
+          <t>https://blog.naver.com/s-beauty06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>326</v>
+        <v>478</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>426</v>
       </c>
       <c r="R4" t="n">
-        <v>356</v>
+        <v>904</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37902943</t>
+          <t>1247940545</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37902943</t>
+          <t>https://m.place.naver.com/place/1247940545</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>주디네일 정발산본점</t>
+          <t>라망네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rkflrkfl1@naver.com</t>
+          <t>ehyeon4862@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1464-0970</t>
+          <t>0507-1409-8266</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
+          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkflrkfl1</t>
+          <t>https://instagram.com/lamain_naily</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>444</v>
+        <v>259</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>465</v>
+        <v>265</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1885034449</t>
+          <t>1819287959</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885034449</t>
+          <t>https://m.place.naver.com/place/1819287959</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S뷰티네일 일산주엽점</t>
+          <t>포쉬네일 홈플러스킨텍스점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>s-beauty06@naver.com</t>
+          <t>lucyjuni@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-9513</t>
+          <t>0507-1333-4281</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
+          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s-beauty06</t>
+          <t>http://www.instagram.com/forsynail_kintex</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="Q6" t="n">
-        <v>426</v>
+        <v>69</v>
       </c>
       <c r="R6" t="n">
-        <v>904</v>
+        <v>532</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1247940545</t>
+          <t>1485591782</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247940545</t>
+          <t>https://m.place.naver.com/place/1485591782</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일스튜디오하몽</t>
+          <t>네일디어원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>laviedekey@naver.com</t>
+          <t>eee2sia@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1480-0355</t>
+          <t>0507-1417-4781</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
+          <t>https://pf.kakao.com/_xlCxgxbG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
-        <v>609</v>
+        <v>968</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1865813904</t>
+          <t>1054380281</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865813904</t>
+          <t>https://m.place.naver.com/place/1054380281</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>포쉬네일 뉴코아아울렛일산점</t>
+          <t>마이유네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>p_yoojin@naver.com</t>
+          <t>tasha81@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1486-0212</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
+          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_madu</t>
+          <t>https://www.instagram.com/my_u_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>485</v>
+        <v>62</v>
       </c>
       <c r="Q8" t="n">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>607</v>
+        <v>64</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1089108291</t>
+          <t>2037646051</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089108291</t>
+          <t>https://m.place.naver.com/place/2037646051</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>렐라네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ksy3315@naver.com</t>
+          <t>cinderellais@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1385-4858</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ree_</t>
+          <t>https://www.instagram.com/rella_nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>315</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>402</v>
+        <v>7</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1653728375</t>
+          <t>1949626855</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653728375</t>
+          <t>https://m.place.naver.com/place/1949626855</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라망네일</t>
+          <t>디엘 네일앤뷰티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ehyeon4862@naver.com</t>
+          <t>soms0m@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1409-8266</t>
+          <t>0507-1392-5930</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
+          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://instagram.com/lamain_naily</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1369,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1819287959</t>
+          <t>2001645591</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819287959</t>
+          <t>https://m.place.naver.com/place/2001645591</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1402,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>발톱닥터</t>
+          <t>오오비 네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jallana@naver.com</t>
+          <t>dltmdgus1206@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1409-8838</t>
+          <t>0507-1332-3495</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
+          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bt_doctor</t>
+          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="Q11" t="n">
-        <v>324</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>479</v>
+        <v>75</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36651631</t>
+          <t>2008508308</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36651631</t>
+          <t>https://m.place.naver.com/place/2008508308</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>홀리네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>ko3hi@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1418-7723</t>
+          <t>0507-1353-4205</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada._.nail/</t>
+          <t>https://www.instagram.com/holy._.nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1561,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>103</v>
+        <v>433</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1226786349</t>
+          <t>37849636</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226786349</t>
+          <t>https://m.place.naver.com/place/37849636</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1598,34 +1590,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>네일르엘</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>youngnail0121@naver.com</t>
+          <t>apoco123@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1411-7300</t>
+          <t>0507-1371-6033</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youngnail0121</t>
+          <t>http://pf.kakao.com/_xaLFXG/chat</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1646,7 +1638,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>786</v>
+        <v>308</v>
       </c>
       <c r="Q13" t="n">
-        <v>287</v>
+        <v>51</v>
       </c>
       <c r="R13" t="n">
-        <v>1073</v>
+        <v>359</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13464862</t>
+          <t>1006093671</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13464862</t>
+          <t>https://m.place.naver.com/place/1006093671</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>홀리네일</t>
+          <t>네일 바이 무제</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ko3hi@naver.com</t>
+          <t>a4001a@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1353-4205</t>
+          <t>0507-1330-5463</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
+          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/holy._.nail</t>
+          <t>https://www.instagram.com/nails_by_mooze</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>227</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="n">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="R14" t="n">
-        <v>433</v>
+        <v>128</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37849636</t>
+          <t>1593406269</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37849636</t>
+          <t>https://m.place.naver.com/place/1593406269</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>물들다, 네일</t>
+          <t>네일 드 제니</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>norajo89@naver.com</t>
+          <t>hja1213@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1472-1621</t>
+          <t>0507-1416-4932</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
+          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_de_jeny</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1834,7 +1826,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1843,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2066663730</t>
+          <t>1635177150</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066663730</t>
+          <t>https://m.place.naver.com/place/1635177150</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1880,48 +1872,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>르네상스</t>
+          <t>네일,숩</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>suny6668@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>support@herren.co.kr</t>
-        </is>
-      </c>
+          <t>hyunjju1541@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1406-4890</t>
+          <t>0507-1325-8243</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
+          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/166708</t>
+          <t>https://www.instagram.com/nail___soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1932,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1941,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>511</v>
+        <v>146</v>
       </c>
       <c r="Q16" t="n">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>760</v>
+        <v>151</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1956,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>468197702</t>
+          <t>1126898433</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/468197702</t>
+          <t>https://m.place.naver.com/place/1126898433</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1978,35 +1966,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>마이유네일</t>
+          <t>리아네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tasha81@naver.com</t>
+          <t>ryddltptkd1401@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1356-7914</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
+          <t>경기도 고양시 일산서구 하이파크로 113 아이파크 1단지 상가동 201호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/my_u_nail</t>
+          <t>https://toss.place/_lb/TYe5QWRPu</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2022,7 +2014,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2031,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="R17" t="n">
-        <v>63</v>
+        <v>235</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2037646051</t>
+          <t>1188570648</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037646051</t>
+          <t>https://m.place.naver.com/place/1188570648</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>라미살롱</t>
+          <t>레몬네일 풍동점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>marsfive@naver.com</t>
+          <t>n-young-@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1386-1988</t>
+          <t>0507-1311-3135</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
+          <t>경기도 고양시 일산동구 숲속마을1로 29-37 서광미르프라자 102호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rami_salon88</t>
+          <t>http://www.instagram.com/lemonshop_diary</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2125,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>701</v>
+        <v>593</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>762</v>
+        <v>597</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1314158350</t>
+          <t>1457328873</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314158350</t>
+          <t>https://m.place.naver.com/place/1457328873</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2162,29 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>엄네일</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>molly32@naver.com</t>
+          <t>youngnail0121@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1333-3487</t>
+          <t>0507-1411-7300</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 39 대양빌딩 6층 602호 베이뷰티 엄네일</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/umnail.__</t>
+          <t>https://www.instagram.com/youngnail0121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2219,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>541</v>
+        <v>788</v>
       </c>
       <c r="Q19" t="n">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="R19" t="n">
-        <v>603</v>
+        <v>1075</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1924027006</t>
+          <t>13464862</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924027006</t>
+          <t>https://m.place.naver.com/place/13464862</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2256,30 +2248,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>어썸네일</t>
+          <t>레푸스 일산장항점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>loves0226@naver.com</t>
+          <t>yoonaejang@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1395-4179</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zCyUG/friend</t>
+          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2289,7 +2285,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,17 +2301,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>68</v>
+        <v>1923</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>645</v>
       </c>
       <c r="R20" t="n">
-        <v>98</v>
+        <v>2568</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1080419201</t>
+          <t>90030989</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080419201</t>
+          <t>https://m.place.naver.com/place/90030989</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2346,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>제제샵</t>
+          <t>온네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rowjddms2@naver.com</t>
+          <t>guswnwnwn@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1395-0132</t>
+          <t>0507-1347-5700</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/all.beauty_jeje</t>
+          <t>https://www.instagram.com/onnail__</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2403,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>367</v>
+        <v>1759</v>
       </c>
       <c r="Q21" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="R21" t="n">
-        <v>451</v>
+        <v>1776</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1262615516</t>
+          <t>31298365</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262615516</t>
+          <t>https://m.place.naver.com/place/31298365</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2440,34 +2436,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>바이마이네일</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jjeong_1004_@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1303-0274</t>
+          <t>0507-1385-4858</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymynail_</t>
+          <t>https://www.instagram.com/nail_ree_</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2477,7 +2473,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2497,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>191</v>
+        <v>315</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="R22" t="n">
-        <v>196</v>
+        <v>402</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2508,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1712300996</t>
+          <t>1653728375</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712300996</t>
+          <t>https://m.place.naver.com/place/1653728375</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2534,25 +2530,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>토리네일</t>
+          <t>원네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>torinail9994@naver.com</t>
+          <t>ohnyoou@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1395-3817</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
+          <t>경기도 고양시 일산서구 탄현로 144-27 2층 202호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/torinail9994</t>
+          <t>https://www.instagram.com/one_nail21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="Q23" t="n">
-        <v>179</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2602,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1327373273</t>
+          <t>2040723368</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327373273</t>
+          <t>https://m.place.naver.com/place/2040723368</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2624,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
+          <t>네일무아</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>garinh_56@naver.com</t>
+          <t>loowowool@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>031-815-3435</t>
+          <t>0507-1322-4700</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://instagram.com/salondeluce_</t>
+          <t>https://www.instagram.com/nail_mua_</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>427</v>
+        <v>89</v>
       </c>
       <c r="Q24" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>515</v>
+        <v>89</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1385267282</t>
+          <t>2028306533</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1385267282</t>
+          <t>https://m.place.naver.com/place/2028306533</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>원네일</t>
+          <t>발톱닥터</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ohnyoou@naver.com</t>
+          <t>jallana@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1395-3817</t>
+          <t>0507-1409-8838</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 탄현로 144-27 2층 202호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/one_nail21</t>
+          <t>https://www.instagram.com/bt_doctor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="R25" t="n">
-        <v>86</v>
+        <v>479</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2040723368</t>
+          <t>36651631</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040723368</t>
+          <t>https://m.place.naver.com/place/36651631</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2812,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일피다</t>
+          <t>네일리쉬</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>apple0879@naver.com</t>
+          <t>moonnsleep@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1495-6782</t>
+          <t>0507-1384-3764</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 산두로 157 네일피다</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hSTxeG</t>
+          <t>http://pf.kakao.com/_CRNHxd</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1164237548</t>
+          <t>1946279327</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164237548</t>
+          <t>https://m.place.naver.com/place/1946279327</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2906,29 +2906,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>뮤트뷰티</t>
+          <t>쏘야네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mute_e@naver.com</t>
+          <t>dlthdus1541@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1410-0371</t>
+          <t>0507-1377-6460</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mute_e</t>
+          <t>https://blog.naver.com/dlthdus1541</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>218</v>
+        <v>442</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="R27" t="n">
-        <v>233</v>
+        <v>661</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2978,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1641314586</t>
+          <t>1952042243</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641314586</t>
+          <t>https://m.place.naver.com/place/1952042243</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3000,29 +3000,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일앤스타일</t>
+          <t>칙스네일 일산백석점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nailnstyle_@naver.com</t>
+          <t>chixs_nail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1438-5770</t>
+          <t>0507-1324-6973</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
+          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nstyle_lab</t>
+          <t>https://www.instagram.com/chixsnail_</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3037</v>
+        <v>1183</v>
       </c>
       <c r="Q28" t="n">
-        <v>830</v>
+        <v>87</v>
       </c>
       <c r="R28" t="n">
-        <v>3867</v>
+        <v>1270</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,17 +3072,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>31424432</t>
+          <t>1834147957</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31424432</t>
+          <t>https://m.place.naver.com/place/1834147957</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3094,29 +3094,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>무이네일</t>
+          <t>조조네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>baeyou0417@naver.com</t>
+          <t>pulin0114@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1351-6051</t>
+          <t>0507-1307-3090</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
+          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muinail_</t>
+          <t>https://www.instagram.com/jojonail.official</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>218</v>
+        <v>46</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R29" t="n">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3166,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1218582286</t>
+          <t>1911173276</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218582286</t>
+          <t>https://m.place.naver.com/place/1911173276</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3188,29 +3188,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일 바이 무제</t>
+          <t>뮤트뷰티</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>onesun012@naver.com</t>
+          <t>mute_e@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1330-5463</t>
+          <t>0507-1410-0371</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nails_by_mooze</t>
+          <t>https://blog.naver.com/mute_e</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="Q30" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1593406269</t>
+          <t>1641314586</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593406269</t>
+          <t>https://m.place.naver.com/place/1641314586</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3282,29 +3282,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일_하니</t>
+          <t>더블앤뷰티 레푸스 일산주엽점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lunefronde@naver.com</t>
+          <t>x7x7x7love@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1490-1526</t>
+          <t>0507-1337-3327</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnDQmn/chat</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>201</v>
+        <v>422</v>
       </c>
       <c r="Q31" t="n">
-        <v>71</v>
+        <v>389</v>
       </c>
       <c r="R31" t="n">
-        <v>272</v>
+        <v>811</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,17 +3354,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2076477973</t>
+          <t>1209456950</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076477973</t>
+          <t>https://m.place.naver.com/place/1209456950</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3376,39 +3376,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>리아네일</t>
+          <t>네일, 또 놀자</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ryddltptkd1401@naver.com</t>
+          <t>dmsquf7541@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1356-7914</t>
+          <t>0507-1377-6207</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크로 113 아이파크 1단지 상가동 201호</t>
+          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYe5QWRPu</t>
+          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3424,7 +3424,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>163</v>
+        <v>388</v>
       </c>
       <c r="Q32" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="R32" t="n">
-        <v>235</v>
+        <v>415</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,17 +3448,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1188570648</t>
+          <t>1416423106</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188570648</t>
+          <t>https://m.place.naver.com/place/1416423106</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3470,29 +3470,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일 드 제니</t>
+          <t>토리네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hja1213@naver.com</t>
+          <t>torinail9994@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1416-4932</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_jeny</t>
+          <t>http://www.instagram.com/torinail9994</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3518,7 +3514,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3527,13 +3523,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>146</v>
+        <v>24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="R33" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,17 +3538,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1635177150</t>
+          <t>1327373273</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1635177150</t>
+          <t>https://m.place.naver.com/place/1327373273</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3564,29 +3560,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일누와</t>
+          <t>네일_하니</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>astro_sexy@naver.com</t>
+          <t>lunefronde@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1355-6322</t>
+          <t>0507-1490-1526</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ClIdn/chat</t>
+          <t>http://pf.kakao.com/_xnDQmn/chat</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3621,13 +3617,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="R34" t="n">
-        <v>190</v>
+        <v>274</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,17 +3632,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1005319723</t>
+          <t>2076477973</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005319723</t>
+          <t>https://m.place.naver.com/place/2076477973</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3658,34 +3654,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일스콘</t>
+          <t>포쉬네일 뉴코아아울렛일산점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>alizee8@naver.com</t>
+          <t>p_yoojin@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1384-0383</t>
+          <t>0507-1486-0212</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
+          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sTlxmG</t>
+          <t>https://www.instagram.com/forsynail_madu</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3706,7 +3702,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3715,13 +3711,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>286</v>
+        <v>489</v>
       </c>
       <c r="Q35" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="R35" t="n">
-        <v>364</v>
+        <v>611</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,17 +3726,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1345185463</t>
+          <t>1089108291</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345185463</t>
+          <t>https://m.place.naver.com/place/1089108291</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3752,34 +3748,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일리쉬</t>
+          <t>오니뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>moonnsleep@naver.com</t>
+          <t>onibeauty@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1384-3764</t>
+          <t>0507-1486-0275</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_CRNHxd</t>
+          <t>https://www.instagram.com/_onibeauty_/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3800,7 +3796,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3809,13 +3805,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>242</v>
+        <v>1031</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>441</v>
       </c>
       <c r="R36" t="n">
-        <v>272</v>
+        <v>1472</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,17 +3820,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1946279327</t>
+          <t>1717534756</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946279327</t>
+          <t>https://m.place.naver.com/place/1717534756</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3846,29 +3842,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아토네일스튜디오 일산</t>
+          <t>두루네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sesehhh@naver.com</t>
+          <t>wngjstodrkr@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1461-2141</t>
+          <t>0507-1328-2941</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 119호 두루네일</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wngjstodrkr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3878,12 +3874,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3894,22 +3890,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>924</v>
+        <v>529</v>
       </c>
       <c r="Q37" t="n">
-        <v>541</v>
+        <v>129</v>
       </c>
       <c r="R37" t="n">
-        <v>1465</v>
+        <v>658</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,17 +3914,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1419778439</t>
+          <t>1944067140</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419778439</t>
+          <t>https://m.place.naver.com/place/1944067140</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -3940,29 +3936,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>츠키네일</t>
+          <t>기린네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>minvl@naver.com</t>
+          <t>ssso131@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1328-9708</t>
+          <t>0507-1468-7932</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thuki_nail/</t>
+          <t>https://www.instagram.com/kirrin_nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3997,13 +3993,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>343</v>
+        <v>115</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="R38" t="n">
-        <v>345</v>
+        <v>170</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4012,17 +4008,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1363998342</t>
+          <t>1349667462</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363998342</t>
+          <t>https://m.place.naver.com/place/1349667462</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4034,29 +4030,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>봄꽃네일</t>
+          <t>뮤다네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>molly32@naver.com</t>
+          <t>bbakyang@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1350-7728</t>
+          <t>0507-1389-7130</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 대화2로 137 상가건물 2층 209호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/myuda_nail/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4066,7 +4062,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4087,17 +4083,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="Q39" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>443</v>
+        <v>289</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4106,17 +4102,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1461994183</t>
+          <t>1129578077</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461994183</t>
+          <t>https://m.place.naver.com/place/1129578077</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4128,34 +4124,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일로희</t>
+          <t>네일브랜디 일산킨텍스점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>younglia_@naver.com</t>
+          <t>ssso131@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1349-2502</t>
+          <t>0507-1325-6774</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlXLKn</t>
+          <t>https://www.instagram.com/nail_b_randy</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4176,7 +4172,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4185,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="Q40" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="R40" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4200,17 +4196,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1049597572</t>
+          <t>1125128328</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049597572</t>
+          <t>https://m.place.naver.com/place/1125128328</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4222,34 +4218,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일디어원</t>
+          <t>라온네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>eee2sia@naver.com</t>
+          <t>yutin60537@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1417-4781</t>
+          <t>0507-1463-2316</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
+          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlCxgxbG</t>
+          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4279,13 +4275,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>890</v>
+        <v>553</v>
       </c>
       <c r="Q41" t="n">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="R41" t="n">
-        <v>961</v>
+        <v>690</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4294,17 +4290,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1054380281</t>
+          <t>1105591278</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054380281</t>
+          <t>https://m.place.naver.com/place/1105591278</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4316,34 +4312,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>허앤밀네일 일산본점</t>
+          <t>네일스튜디오하몽</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>laviedekey@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1387-0713</t>
+          <t>0507-1480-0355</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heo_mil_nail</t>
+          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4364,7 +4360,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4373,13 +4369,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1104</v>
+        <v>585</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="R42" t="n">
-        <v>1110</v>
+        <v>609</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4388,17 +4384,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1482502953</t>
+          <t>1865813904</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482502953</t>
+          <t>https://m.place.naver.com/place/1865813904</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4410,34 +4406,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>기린네일</t>
+          <t>아르다뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1468-7932</t>
+          <t>0507-1354-1704</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kirrin_nail</t>
+          <t>https://pf.kakao.com/_qJhgb</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4458,7 +4454,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4467,13 +4463,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="Q43" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="R43" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4482,17 +4478,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1349667462</t>
+          <t>1958887188</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349667462</t>
+          <t>https://m.place.naver.com/place/1958887188</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4504,34 +4500,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일르엘</t>
+          <t>네일앤스타일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>apoco123@naver.com</t>
+          <t>nailnstyle_@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1371-6033</t>
+          <t>0507-1438-5770</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaLFXG/chat</t>
+          <t>https://www.instagram.com/nstyle_lab</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4552,7 +4548,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4561,13 +4557,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>304</v>
+        <v>3036</v>
       </c>
       <c r="Q44" t="n">
-        <v>51</v>
+        <v>830</v>
       </c>
       <c r="R44" t="n">
-        <v>355</v>
+        <v>3866</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4576,17 +4572,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1006093671</t>
+          <t>31424432</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006093671</t>
+          <t>https://m.place.naver.com/place/31424432</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4598,34 +4594,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>쏘야네일</t>
+          <t>네일누와</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dlthdus1541@naver.com</t>
+          <t>astro_sexy@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1377-6460</t>
+          <t>0507-1355-6322</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlthdus1541</t>
+          <t>http://pf.kakao.com/_ClIdn/chat</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4635,7 +4631,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4646,7 +4642,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4655,13 +4651,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>442</v>
+        <v>167</v>
       </c>
       <c r="Q45" t="n">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="R45" t="n">
-        <v>661</v>
+        <v>190</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4670,17 +4666,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1952042243</t>
+          <t>1005319723</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952042243</t>
+          <t>https://m.place.naver.com/place/1005319723</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4692,44 +4688,48 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
+          <t>르네상스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jujunail0713@naver.com</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>suny6668@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>support@herren.co.kr</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1404-4143</t>
+          <t>0507-1406-4890</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pediheal_ilsan</t>
+          <t>https://booking.naver.com/booking/13/bizes/166708</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4740,7 +4740,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>210</v>
+        <v>511</v>
       </c>
       <c r="Q46" t="n">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="R46" t="n">
-        <v>485</v>
+        <v>760</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4764,17 +4764,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13092675</t>
+          <t>468197702</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13092675</t>
+          <t>https://m.place.naver.com/place/468197702</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4786,29 +4786,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>레몬네일 풍동점</t>
+          <t>별빛네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>n-young-@naver.com</t>
+          <t>naminail@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1311-3135</t>
+          <t>0507-1311-0283</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을1로 29-37 서광미르프라자 102호</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/lemonshop_diary</t>
+          <t>https://www.instagram.com/_byeolbit_nail/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>592</v>
+        <v>252</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R47" t="n">
-        <v>596</v>
+        <v>263</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4858,17 +4858,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1457328873</t>
+          <t>2011766876</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1457328873</t>
+          <t>https://m.place.naver.com/place/2011766876</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4880,29 +4880,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>모던네일</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>modern_nail@naver.com</t>
+          <t>mimisuji52@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1381-4140</t>
+          <t>0507-1416-6295</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 1층 136호</t>
+          <t>경기도 고양시 일산서구 고양대로 685</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mdna_il</t>
+          <t>https://blog.naver.com/mimisuji52</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4928,7 +4928,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4937,13 +4937,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="Q48" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="R48" t="n">
-        <v>313</v>
+        <v>112</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4952,17 +4952,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1882656587</t>
+          <t>1952745044</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882656587</t>
+          <t>https://m.place.naver.com/place/1952745044</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4974,29 +4974,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>운디아네일</t>
+          <t>무이네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>undia10@naver.com</t>
+          <t>baeyou0417@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1327-8629</t>
+          <t>0507-1351-6051</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/undia_nail</t>
+          <t>https://www.instagram.com/muinail_</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5031,13 +5031,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1822</v>
+        <v>219</v>
       </c>
       <c r="Q49" t="n">
-        <v>166</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>1988</v>
+        <v>222</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5046,17 +5046,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1192977296</t>
+          <t>1218582286</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192977296</t>
+          <t>https://m.place.naver.com/place/1218582286</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5068,29 +5068,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일팩토리</t>
+          <t>네일은뷰티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nailfactory13@naver.com</t>
+          <t>topnailjina@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1323-3381</t>
+          <t>0507-1393-0807</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
+          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https:///linktr.ee/Nail_Factory13</t>
+          <t>https://www.instagram.com/nail_eunbeauty</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5116,7 +5116,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5125,13 +5125,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1022</v>
+        <v>445</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R50" t="n">
-        <v>1032</v>
+        <v>549</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5140,17 +5140,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1383137709</t>
+          <t>1421368108</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383137709</t>
+          <t>https://m.place.naver.com/place/1421368108</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5162,34 +5162,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>레푸스 일산장항점</t>
+          <t>네일뮤토</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>yoonaejang@naver.com</t>
+          <t>ithgml123@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1395-4179</t>
+          <t>0507-1370-0857</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
+          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
+          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5210,22 +5210,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1922</v>
+        <v>10</v>
       </c>
       <c r="Q51" t="n">
-        <v>645</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>2567</v>
+        <v>15</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5234,17 +5234,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>90030989</t>
+          <t>1260058171</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/90030989</t>
+          <t>https://m.place.naver.com/place/1260058171</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5256,29 +5256,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일맑음래쉬</t>
+          <t>물들다, 네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rlazzzzzz@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1356-7749</t>
+          <t>0507-1472-1621</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
+          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="R52" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5328,17 +5328,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1604742986</t>
+          <t>2066663730</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604742986</t>
+          <t>https://m.place.naver.com/place/2066663730</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5350,34 +5350,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>소울메이트네일샵</t>
+          <t>비온네일 일산킨텍스점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>algmlspdlf@naver.com</t>
+          <t>feb_7th@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1382-5531</t>
+          <t>0507-1384-4180</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/soulmatenail</t>
+          <t>http://pf.kakao.com/_HDxnPn</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5398,7 +5398,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>229</v>
+        <v>78</v>
       </c>
       <c r="Q53" t="n">
-        <v>163</v>
+        <v>36</v>
       </c>
       <c r="R53" t="n">
-        <v>392</v>
+        <v>114</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5422,17 +5422,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>36620432</t>
+          <t>1988141515</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36620432</t>
+          <t>https://m.place.naver.com/place/1988141515</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5444,34 +5444,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>오니뷰티 네일&amp;속눈썹</t>
+          <t>네일스콘</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>onibeauty@naver.com</t>
+          <t>alizee8@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1486-0275</t>
+          <t>0507-1384-0383</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
+          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onibeauty_/</t>
+          <t>http://pf.kakao.com/_sTlxmG</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5492,7 +5492,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5501,13 +5501,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1030</v>
+        <v>286</v>
       </c>
       <c r="Q54" t="n">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="R54" t="n">
-        <v>1466</v>
+        <v>364</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5516,17 +5516,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1717534756</t>
+          <t>1345185463</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717534756</t>
+          <t>https://m.place.naver.com/place/1345185463</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5538,29 +5538,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>오드네일</t>
+          <t>어썸네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>seong30526@naver.com</t>
+          <t>loves0226@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1368-7567</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
+          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Kfxacn</t>
+          <t>http://pf.kakao.com/_zCyUG/friend</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5595,13 +5591,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="R55" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5610,17 +5606,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026543533</t>
+          <t>1080419201</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026543533</t>
+          <t>https://m.place.naver.com/place/1080419201</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5632,34 +5628,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>제이윤네일</t>
+          <t>네일더무드</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>x7129x@naver.com</t>
+          <t>2skgus7@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1356-0390</t>
+          <t>0507-1417-7531</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1160 4층 411호</t>
+          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_yun__nail?igsh=NDZwZ2wwOWFkZWZm</t>
+          <t>https://pf.kakao.com/_bWPiG</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5680,7 +5676,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5689,13 +5685,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="Q56" t="n">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>504</v>
+        <v>350</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5704,17 +5700,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1373645197</t>
+          <t>1154624160</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373645197</t>
+          <t>https://m.place.naver.com/place/1154624160</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5726,29 +5722,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>포쉬네일 홈플러스킨텍스점</t>
+          <t>라미살롱</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lucyjuni@naver.com</t>
+          <t>marsfive@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1333-4281</t>
+          <t>0507-1386-1988</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/forsynail_kintex</t>
+          <t>https://www.instagram.com/rami_salon88</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5783,13 +5779,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>463</v>
+        <v>702</v>
       </c>
       <c r="Q57" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="R57" t="n">
-        <v>532</v>
+        <v>763</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5798,17 +5794,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1485591782</t>
+          <t>1314158350</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485591782</t>
+          <t>https://m.place.naver.com/place/1314158350</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5820,29 +5816,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>온네일</t>
+          <t>제제샵</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>guswnwnwn@naver.com</t>
+          <t>rowjddms2@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1347-5700</t>
+          <t>0507-1395-0132</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
+          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onnail__</t>
+          <t>http://www.instagram.com/all.beauty_jeje</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5877,13 +5873,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1752</v>
+        <v>367</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="R58" t="n">
-        <v>1769</v>
+        <v>451</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5892,17 +5888,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>31298365</t>
+          <t>1262615516</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31298365</t>
+          <t>https://m.place.naver.com/place/1262615516</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -5914,39 +5910,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제이 뷰티 클리어</t>
+          <t>아토네일스튜디오 일산</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jonghyun0823@naver.com</t>
+          <t>sesehhh@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1342-8831</t>
+          <t>0507-1461-2141</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
+          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBf6NdCd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5962,22 +5958,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>354</v>
+        <v>925</v>
       </c>
       <c r="Q59" t="n">
-        <v>40</v>
+        <v>542</v>
       </c>
       <c r="R59" t="n">
-        <v>394</v>
+        <v>1467</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5986,17 +5982,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1701276497</t>
+          <t>1419778439</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701276497</t>
+          <t>https://m.place.naver.com/place/1419778439</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6008,29 +6004,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>디엘 네일앤뷰티</t>
+          <t>네일바이아르</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>soms0m@naver.com</t>
+          <t>nailbyare@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1392-5930</t>
+          <t>0507-1441-7961</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
+          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailbyare/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6040,7 +6036,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6061,17 +6057,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="Q60" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6080,17 +6076,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2001645591</t>
+          <t>2094840936</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001645591</t>
+          <t>https://m.place.naver.com/place/2094840936</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6102,29 +6098,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일브랜디 일산킨텍스점</t>
+          <t>네일오티디</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>swc1439@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1325-6774</t>
+          <t>0507-1429-0763</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
+          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_b_randy</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6134,7 +6130,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6155,17 +6151,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="Q61" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="R61" t="n">
-        <v>324</v>
+        <v>160</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6174,17 +6170,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1125128328</t>
+          <t>2026395486</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125128328</t>
+          <t>https://m.place.naver.com/place/2026395486</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6196,34 +6192,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일뮤토</t>
+          <t>반스네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ithgml123@naver.com</t>
+          <t>white880704@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1370-0857</t>
+          <t>0507-1323-9981</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
+          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
+          <t>http://pf.kakao.com/_AXAmn</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6244,7 +6240,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6253,13 +6249,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R62" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6268,17 +6264,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1260058171</t>
+          <t>612271526</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260058171</t>
+          <t>https://m.place.naver.com/place/612271526</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6290,29 +6286,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일,숩</t>
+          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>hyunjju1541@naver.com</t>
+          <t>jujunail0713@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1325-8243</t>
+          <t>0507-1404-4143</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___soop</t>
+          <t>https://www.instagram.com/pediheal_ilsan</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6347,13 +6343,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>145</v>
+        <v>209</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="R63" t="n">
-        <v>150</v>
+        <v>485</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6362,17 +6358,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1126898433</t>
+          <t>13092675</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126898433</t>
+          <t>https://m.place.naver.com/place/13092675</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6384,34 +6380,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>비온네일 일산킨텍스점</t>
+          <t>네일맑음래쉬</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>feb_7th@naver.com</t>
+          <t>rlazzzzzz@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1384-4180</t>
+          <t>0507-1356-7749</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HDxnPn</t>
+          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6432,7 +6428,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6441,13 +6437,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="Q64" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="R64" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6456,17 +6452,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1988141515</t>
+          <t>1604742986</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1988141515</t>
+          <t>https://m.place.naver.com/place/1604742986</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6478,34 +6474,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오묘네일</t>
+          <t>오드네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>skme12@naver.com</t>
+          <t>seong30526@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1351-1060</t>
+          <t>0507-1368-7567</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/5.myo_art</t>
+          <t>http://pf.kakao.com/_Kfxacn</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6526,7 +6522,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6535,13 +6531,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>282</v>
+        <v>62</v>
       </c>
       <c r="Q65" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="R65" t="n">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6550,17 +6546,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1036508811</t>
+          <t>2026543533</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036508811</t>
+          <t>https://m.place.naver.com/place/2026543533</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6572,29 +6568,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>조조네일</t>
+          <t>소울메이트네일샵</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yhkim5616lmy@naver.com</t>
+          <t>algmlspdlf@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1307-3090</t>
+          <t>0507-1382-5531</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jojonail.official</t>
+          <t>http://www.instagram.com/soulmatenail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6629,13 +6625,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="Q66" t="n">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="R66" t="n">
-        <v>62</v>
+        <v>392</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6644,17 +6640,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1911173276</t>
+          <t>36620432</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911173276</t>
+          <t>https://m.place.naver.com/place/36620432</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6666,34 +6662,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>더블앤뷰티 레푸스 일산주엽점</t>
+          <t>네일팩토리</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>x7x7x7love@naver.com</t>
+          <t>nailfactory13@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1337-3327</t>
+          <t>0507-1323-3381</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https:///linktr.ee/Nail_Factory13</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6723,13 +6719,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>423</v>
+        <v>1023</v>
       </c>
       <c r="Q67" t="n">
-        <v>389</v>
+        <v>10</v>
       </c>
       <c r="R67" t="n">
-        <v>812</v>
+        <v>1033</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6738,17 +6734,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1209456950</t>
+          <t>1383137709</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209456950</t>
+          <t>https://m.place.naver.com/place/1383137709</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6760,29 +6756,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>그리심네일&amp;뷰티</t>
+          <t>오묘네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>herb2592@naver.com</t>
+          <t>skme12@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1329-7483</t>
+          <t>0507-1351-1060</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
+          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/herb2592</t>
+          <t>http://www.instagram.com/5.myo_art</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6797,7 +6793,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6817,13 +6813,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="Q68" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="R68" t="n">
-        <v>350</v>
+        <v>313</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6832,17 +6828,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1667004401</t>
+          <t>1036508811</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667004401</t>
+          <t>https://m.place.naver.com/place/1036508811</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6854,29 +6850,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>칙스네일 일산백석점</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>chixs_nail@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1324-6973</t>
+          <t>0507-1418-7723</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
+          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chixsnail_</t>
+          <t>https://www.instagram.com/dada._.nail/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6911,13 +6907,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1174</v>
+        <v>81</v>
       </c>
       <c r="Q69" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="R69" t="n">
-        <v>1240</v>
+        <v>103</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6926,17 +6922,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1834147957</t>
+          <t>1226786349</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834147957</t>
+          <t>https://m.place.naver.com/place/1226786349</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -6948,34 +6944,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일더무드</t>
+          <t>운디아네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2skgus7@naver.com</t>
+          <t>undia10@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1417-7531</t>
+          <t>0507-1327-8629</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
+          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_bWPiG</t>
+          <t>http://www.instagram.com/undia_nail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6996,7 +6992,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7005,13 +7001,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>343</v>
+        <v>1823</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="R70" t="n">
-        <v>348</v>
+        <v>1989</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7020,17 +7016,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1154624160</t>
+          <t>1192977296</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154624160</t>
+          <t>https://m.place.naver.com/place/1192977296</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7042,29 +7038,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일무아</t>
+          <t>주디네일 정발산본점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>rkflrkfl1@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1322-4700</t>
+          <t>0507-1464-0970</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
+          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mua_</t>
+          <t>https://blog.naver.com/rkflrkfl1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7079,7 +7075,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7099,13 +7095,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R71" t="n">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7114,17 +7110,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2028306533</t>
+          <t>1885034449</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028306533</t>
+          <t>https://m.place.naver.com/place/1885034449</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7136,29 +7132,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>바이마이네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mimisuji52@naver.com</t>
+          <t>jjeong_1004_@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1416-6295</t>
+          <t>0507-1303-0274</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 685</t>
+          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mimisuji52</t>
+          <t>https://www.instagram.com/bymynail_</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7173,7 +7169,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7193,13 +7189,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="Q72" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>112</v>
+        <v>196</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7208,17 +7204,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1952745044</t>
+          <t>1712300996</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952745044</t>
+          <t>https://m.place.naver.com/place/1712300996</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7230,29 +7226,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일은뷰티</t>
+          <t>제이 뷰티 클리어</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>topnailjina@naver.com</t>
+          <t>jonghyun0823@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1393-0807</t>
+          <t>0507-1342-8831</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
+          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_eunbeauty</t>
+          <t>https://open.kakao.com/o/sBf6NdCd</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7278,7 +7274,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7287,13 +7283,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>443</v>
+        <v>354</v>
       </c>
       <c r="Q73" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="R73" t="n">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7302,17 +7298,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1421368108</t>
+          <t>1701276497</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421368108</t>
+          <t>https://m.place.naver.com/place/1701276497</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7324,29 +7320,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>츠키네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>minvl@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1463-2316</t>
+          <t>0507-1328-9708</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>https://www.instagram.com/thuki_nail/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7372,7 +7368,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7381,13 +7377,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>551</v>
+        <v>343</v>
       </c>
       <c r="Q74" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>688</v>
+        <v>345</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7396,17 +7392,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1105591278</t>
+          <t>1363998342</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105591278</t>
+          <t>https://m.place.naver.com/place/1363998342</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7418,29 +7414,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>우네뜨 네일</t>
+          <t>그리심네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kimsuji0061@naver.com</t>
+          <t>herb2592@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1387-1893</t>
+          <t>0507-1329-7483</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1437 화성프라자 5층 503호</t>
+          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woonette._/profilecard/?igsh=MWNyY29tejFuaXViMA==</t>
+          <t>https://blog.naver.com/herb2592</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7455,7 +7451,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7475,13 +7471,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>49</v>
+        <v>259</v>
       </c>
       <c r="Q75" t="n">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="R75" t="n">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7490,17 +7486,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2054238571</t>
+          <t>1667004401</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054238571</t>
+          <t>https://m.place.naver.com/place/1667004401</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -7512,29 +7508,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일바이아르</t>
+          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nailbyare@naver.com</t>
+          <t>garinh_56@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1441-7961</t>
+          <t>031-815-3435</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
+          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyare/</t>
+          <t>http://instagram.com/salondeluce_</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7569,13 +7565,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>61</v>
+        <v>427</v>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="R76" t="n">
-        <v>66</v>
+        <v>515</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7584,17 +7580,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2094840936</t>
+          <t>1385267282</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094840936</t>
+          <t>https://m.place.naver.com/place/1385267282</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/일산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/일산_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>허앤밀네일 일산본점</t>
+          <t>조조네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>pulin0114@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1387-0713</t>
+          <t>0507-1307-3090</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
+          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heo_mil_nail</t>
+          <t>https://www.instagram.com/jojonail.official</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1106</v>
+        <v>46</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>1112</v>
+        <v>62</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1482502953</t>
+          <t>1911173276</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482502953</t>
+          <t>https://m.place.naver.com/place/1911173276</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일로희</t>
+          <t>W네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>younglia_@naver.com</t>
+          <t>w-nail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1349-2502</t>
+          <t>0507-1436-9888</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 14-4 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlXLKn</t>
+          <t>http://www.instagram.com/wnail1543/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>255</v>
+        <v>124</v>
       </c>
       <c r="Q3" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="R3" t="n">
-        <v>312</v>
+        <v>223</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1049597572</t>
+          <t>37842153</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049597572</t>
+          <t>https://m.place.naver.com/place/37842153</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,34 +752,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S뷰티네일 일산주엽점</t>
+          <t>어썸네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>s-beauty06@naver.com</t>
+          <t>loves0226@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1327-9513</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
+          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s-beauty06</t>
+          <t>http://pf.kakao.com/_zCyUG/friend</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +796,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>478</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="n">
-        <v>426</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
-        <v>904</v>
+        <v>98</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1247940545</t>
+          <t>1080419201</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247940545</t>
+          <t>https://m.place.naver.com/place/1080419201</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라망네일</t>
+          <t>렐라네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ehyeon4862@naver.com</t>
+          <t>cinderellais@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1409-8266</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://instagram.com/lamain_naily</t>
+          <t>https://www.instagram.com/rella_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>259</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>265</v>
+        <v>7</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1819287959</t>
+          <t>1949626855</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819287959</t>
+          <t>https://m.place.naver.com/place/1949626855</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포쉬네일 홈플러스킨텍스점</t>
+          <t>바이마이네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lucyjuni@naver.com</t>
+          <t>jjeong_1004_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1333-4281</t>
+          <t>0507-1303-0274</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
+          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/forsynail_kintex</t>
+          <t>https://www.instagram.com/bymynail_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="Q6" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>532</v>
+        <v>196</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1004,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1485591782</t>
+          <t>1712300996</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485591782</t>
+          <t>https://m.place.naver.com/place/1712300996</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1026,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일디어원</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eee2sia@naver.com</t>
+          <t>youngnail0121@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-4781</t>
+          <t>0507-1411-7300</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlCxgxbG</t>
+          <t>https://www.instagram.com/youngnail0121</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>897</v>
+        <v>788</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>287</v>
       </c>
       <c r="R7" t="n">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1054380281</t>
+          <t>13464862</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054380281</t>
+          <t>https://m.place.naver.com/place/13464862</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,25 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이유네일</t>
+          <t>운디아네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tasha81@naver.com</t>
+          <t>undia10@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1327-8629</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
+          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/my_u_nail</t>
+          <t>http://www.instagram.com/undia_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>62</v>
+        <v>1823</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="R8" t="n">
-        <v>64</v>
+        <v>1989</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2037646051</t>
+          <t>1192977296</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037646051</t>
+          <t>https://m.place.naver.com/place/1192977296</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,30 +1214,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>렐라네일</t>
+          <t>네일더무드</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cinderellais@naver.com</t>
+          <t>2skgus7@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1417-7531</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
+          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rella_nail</t>
+          <t>https://pf.kakao.com/_bWPiG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1262,7 +1262,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>345</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1949626855</t>
+          <t>1154624160</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949626855</t>
+          <t>https://m.place.naver.com/place/1154624160</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>디엘 네일앤뷰티</t>
+          <t>물들다, 네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>soms0m@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1392-5930</t>
+          <t>0507-1472-1621</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
+          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="R10" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2001645591</t>
+          <t>2066663730</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001645591</t>
+          <t>https://m.place.naver.com/place/2066663730</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>오오비 네일</t>
+          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dltmdgus1206@naver.com</t>
+          <t>jujunail0713@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1332-3495</t>
+          <t>0507-1404-4143</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
+          <t>https://www.instagram.com/pediheal_ilsan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>276</v>
       </c>
       <c r="R11" t="n">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2008508308</t>
+          <t>13092675</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2008508308</t>
+          <t>https://m.place.naver.com/place/13092675</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>홀리네일</t>
+          <t>라망네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ko3hi@naver.com</t>
+          <t>ehyeon4862@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1353-4205</t>
+          <t>0507-1409-8266</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
+          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/holy._.nail</t>
+          <t>https://instagram.com/lamain_naily</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>433</v>
+        <v>265</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37849636</t>
+          <t>1819287959</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37849636</t>
+          <t>https://m.place.naver.com/place/1819287959</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,39 +1590,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일르엘</t>
+          <t>아토네일스튜디오 일산</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>apoco123@naver.com</t>
+          <t>sesehhh@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1371-6033</t>
+          <t>0507-1461-2141</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
+          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaLFXG/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1638,22 +1638,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>308</v>
+        <v>925</v>
       </c>
       <c r="Q13" t="n">
-        <v>51</v>
+        <v>542</v>
       </c>
       <c r="R13" t="n">
-        <v>359</v>
+        <v>1467</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1006093671</t>
+          <t>1419778439</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006093671</t>
+          <t>https://m.place.naver.com/place/1419778439</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,29 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일 바이 무제</t>
+          <t>기린네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>a4001a@naver.com</t>
+          <t>ssso131@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1330-5463</t>
+          <t>0507-1468-7932</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nails_by_mooze</t>
+          <t>https://www.instagram.com/kirrin_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q14" t="n">
         <v>55</v>
       </c>
-      <c r="Q14" t="n">
-        <v>73</v>
-      </c>
       <c r="R14" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1593406269</t>
+          <t>1349667462</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593406269</t>
+          <t>https://m.place.naver.com/place/1349667462</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1778,34 +1778,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일 드 제니</t>
+          <t>네일르엘</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hja1213@naver.com</t>
+          <t>apoco123@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1416-4932</t>
+          <t>0507-1371-6033</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_jeny</t>
+          <t>http://pf.kakao.com/_xaLFXG/chat</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>150</v>
+        <v>308</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="R15" t="n">
-        <v>151</v>
+        <v>359</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1635177150</t>
+          <t>1006093671</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1635177150</t>
+          <t>https://m.place.naver.com/place/1006093671</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,34 +1872,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일,숩</t>
+          <t>네일리쉬</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hyunjju1541@naver.com</t>
+          <t>moonnsleep@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1325-8243</t>
+          <t>0507-1384-3764</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___soop</t>
+          <t>http://pf.kakao.com/_CRNHxd</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1920,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="R16" t="n">
-        <v>151</v>
+        <v>272</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1126898433</t>
+          <t>1946279327</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126898433</t>
+          <t>https://m.place.naver.com/place/1946279327</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2060,34 +2060,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>레몬네일 풍동점</t>
+          <t>더블앤뷰티 레푸스 일산주엽점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>n-young-@naver.com</t>
+          <t>x7x7x7love@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1311-3135</t>
+          <t>0507-1337-3327</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을1로 29-37 서광미르프라자 102호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/lemonshop_diary</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2108,7 +2108,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>593</v>
+        <v>422</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>388</v>
       </c>
       <c r="R18" t="n">
-        <v>597</v>
+        <v>810</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1457328873</t>
+          <t>1209456950</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1457328873</t>
+          <t>https://m.place.naver.com/place/1209456950</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2154,29 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>오오비 네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>youngnail0121@naver.com</t>
+          <t>dltmdgus1206@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1411-7300</t>
+          <t>0507-1332-3495</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
+          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youngnail0121</t>
+          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>788</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="n">
-        <v>287</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>1075</v>
+        <v>75</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13464862</t>
+          <t>2008508308</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13464862</t>
+          <t>https://m.place.naver.com/place/2008508308</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2248,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>레푸스 일산장항점</t>
+          <t>뮤다네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yoonaejang@naver.com</t>
+          <t>bbakyang@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1395-4179</t>
+          <t>0507-1389-7130</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
+          <t>https://www.instagram.com/myuda_nail/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2296,22 +2296,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1923</v>
+        <v>285</v>
       </c>
       <c r="Q20" t="n">
-        <v>645</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>2568</v>
+        <v>290</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>90030989</t>
+          <t>1129578077</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/90030989</t>
+          <t>https://m.place.naver.com/place/1129578077</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2342,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>온네일</t>
+          <t>네일, 또 놀자</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>guswnwnwn@naver.com</t>
+          <t>dmsquf7541@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1347-5700</t>
+          <t>0507-1377-6207</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
+          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onnail__</t>
+          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1759</v>
+        <v>388</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R21" t="n">
-        <v>1776</v>
+        <v>415</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>31298365</t>
+          <t>1416423106</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31298365</t>
+          <t>https://m.place.naver.com/place/1416423106</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2436,34 +2436,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>네일스콘</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>alizee8@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1385-4858</t>
+          <t>0507-1384-0383</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
+          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ree_</t>
+          <t>http://pf.kakao.com/_sTlxmG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2484,7 +2484,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="Q22" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="R22" t="n">
-        <v>402</v>
+        <v>364</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1653728375</t>
+          <t>1345185463</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653728375</t>
+          <t>https://m.place.naver.com/place/1345185463</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2530,29 +2530,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>원네일</t>
+          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ohnyoou@naver.com</t>
+          <t>garinh_56@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1395-3817</t>
+          <t>031-815-3435</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 탄현로 144-27 2층 202호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/one_nail21</t>
+          <t>http://instagram.com/salondeluce_</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>84</v>
+        <v>427</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="R23" t="n">
-        <v>86</v>
+        <v>515</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2040723368</t>
+          <t>1385267282</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040723368</t>
+          <t>https://m.place.naver.com/place/1385267282</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2624,34 +2624,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일무아</t>
+          <t>네일_하니</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>lunefronde@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1322-4700</t>
+          <t>0507-1490-1526</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mua_</t>
+          <t>http://pf.kakao.com/_xnDQmn/chat</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2672,7 +2672,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>89</v>
+        <v>203</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="R24" t="n">
-        <v>89</v>
+        <v>274</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2028306533</t>
+          <t>2076477973</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028306533</t>
+          <t>https://m.place.naver.com/place/2076477973</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2718,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>발톱닥터</t>
+          <t>그리심네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jallana@naver.com</t>
+          <t>herb2592@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1409-8838</t>
+          <t>0507-1329-7483</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
+          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bt_doctor</t>
+          <t>https://blog.naver.com/herb2592</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>155</v>
+        <v>259</v>
       </c>
       <c r="Q25" t="n">
-        <v>324</v>
+        <v>91</v>
       </c>
       <c r="R25" t="n">
-        <v>479</v>
+        <v>350</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36651631</t>
+          <t>1667004401</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36651631</t>
+          <t>https://m.place.naver.com/place/1667004401</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2812,34 +2812,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일리쉬</t>
+          <t>네일,숩</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>moonnsleep@naver.com</t>
+          <t>hyunjju1541@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1384-3764</t>
+          <t>0507-1325-8243</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
+          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_CRNHxd</t>
+          <t>https://www.instagram.com/nail___soop</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2860,7 +2860,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2869,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>272</v>
+        <v>151</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1946279327</t>
+          <t>1126898433</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946279327</t>
+          <t>https://m.place.naver.com/place/1126898433</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2906,29 +2906,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>쏘야네일</t>
+          <t>네일앤스타일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dlthdus1541@naver.com</t>
+          <t>nailnstyle_@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1377-6460</t>
+          <t>0507-1438-5770</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlthdus1541</t>
+          <t>https://www.instagram.com/nstyle_lab</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>442</v>
+        <v>3036</v>
       </c>
       <c r="Q27" t="n">
-        <v>219</v>
+        <v>830</v>
       </c>
       <c r="R27" t="n">
-        <v>661</v>
+        <v>3866</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1952042243</t>
+          <t>31424432</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952042243</t>
+          <t>https://m.place.naver.com/place/31424432</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3000,44 +3000,48 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>칙스네일 일산백석점</t>
+          <t>르네상스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>chixs_nail@naver.com</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>suny6668@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>support@herren.co.kr</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1324-6973</t>
+          <t>0507-1406-4890</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chixsnail_</t>
+          <t>https://booking.naver.com/booking/13/bizes/166708</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3048,7 +3052,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3057,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1183</v>
+        <v>511</v>
       </c>
       <c r="Q28" t="n">
-        <v>87</v>
+        <v>249</v>
       </c>
       <c r="R28" t="n">
-        <v>1270</v>
+        <v>760</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,12 +3076,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1834147957</t>
+          <t>468197702</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834147957</t>
+          <t>https://m.place.naver.com/place/468197702</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3094,34 +3098,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>조조네일</t>
+          <t>아르다뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pulin0114@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1307-3090</t>
+          <t>0507-1354-1704</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jojonail.official</t>
+          <t>https://pf.kakao.com/_qJhgb</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3142,7 +3146,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3151,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="R29" t="n">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,12 +3170,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1911173276</t>
+          <t>1958887188</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911173276</t>
+          <t>https://m.place.naver.com/place/1958887188</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3188,29 +3192,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뮤트뷰티</t>
+          <t>네일브랜디 일산킨텍스점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mute_e@naver.com</t>
+          <t>ssso131@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1410-0371</t>
+          <t>0507-1325-6774</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mute_e</t>
+          <t>https://www.instagram.com/nail_b_randy</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3225,7 +3229,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3245,13 +3249,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="R30" t="n">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,12 +3264,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1641314586</t>
+          <t>1125128328</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641314586</t>
+          <t>https://m.place.naver.com/place/1125128328</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3282,34 +3286,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>더블앤뷰티 레푸스 일산주엽점</t>
+          <t>네일팩토리</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>x7x7x7love@naver.com</t>
+          <t>nailfactory13@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1337-3327</t>
+          <t>0507-1323-3381</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https:///linktr.ee/Nail_Factory13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3339,13 +3343,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>422</v>
+        <v>1023</v>
       </c>
       <c r="Q31" t="n">
-        <v>389</v>
+        <v>10</v>
       </c>
       <c r="R31" t="n">
-        <v>811</v>
+        <v>1033</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,12 +3358,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1209456950</t>
+          <t>1383137709</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209456950</t>
+          <t>https://m.place.naver.com/place/1383137709</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3376,34 +3380,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일, 또 놀자</t>
+          <t>반스네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dmsquf7541@naver.com</t>
+          <t>white880704@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1377-6207</t>
+          <t>0507-1323-9981</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
+          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
+          <t>http://pf.kakao.com/_AXAmn</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3424,7 +3428,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3433,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>388</v>
+        <v>67</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="R32" t="n">
-        <v>415</v>
+        <v>76</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,12 +3452,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1416423106</t>
+          <t>612271526</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1416423106</t>
+          <t>https://m.place.naver.com/place/612271526</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3470,25 +3474,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>토리네일</t>
+          <t>S뷰티네일 일산주엽점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>torinail9994@naver.com</t>
+          <t>s-beauty06@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1327-9513</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/torinail9994</t>
+          <t>https://blog.naver.com/s-beauty06</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3503,7 +3511,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3519,17 +3527,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>24</v>
+        <v>478</v>
       </c>
       <c r="Q33" t="n">
-        <v>179</v>
+        <v>426</v>
       </c>
       <c r="R33" t="n">
-        <v>203</v>
+        <v>904</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,12 +3546,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1327373273</t>
+          <t>1247940545</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327373273</t>
+          <t>https://m.place.naver.com/place/1247940545</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3560,29 +3568,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일_하니</t>
+          <t>네일디어원</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lunefronde@naver.com</t>
+          <t>eee2sia@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1490-1526</t>
+          <t>0507-1417-4781</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnDQmn/chat</t>
+          <t>https://pf.kakao.com/_xlCxgxbG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3617,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>203</v>
+        <v>897</v>
       </c>
       <c r="Q34" t="n">
         <v>71</v>
       </c>
       <c r="R34" t="n">
-        <v>274</v>
+        <v>968</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,12 +3640,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2076477973</t>
+          <t>1054380281</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076477973</t>
+          <t>https://m.place.naver.com/place/1054380281</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3654,29 +3662,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>포쉬네일 뉴코아아울렛일산점</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>p_yoojin@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1486-0212</t>
+          <t>0507-1418-7723</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
+          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_madu</t>
+          <t>https://www.instagram.com/dada._.nail/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3711,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="Q35" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="R35" t="n">
-        <v>611</v>
+        <v>103</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,12 +3734,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1089108291</t>
+          <t>1226786349</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089108291</t>
+          <t>https://m.place.naver.com/place/1226786349</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3748,34 +3756,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오니뷰티 네일&amp;속눈썹</t>
+          <t>비온네일 일산킨텍스점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>onibeauty@naver.com</t>
+          <t>feb_7th@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1486-0275</t>
+          <t>0507-1384-4180</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onibeauty_/</t>
+          <t>http://pf.kakao.com/_HDxnPn</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3796,7 +3804,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3805,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1031</v>
+        <v>78</v>
       </c>
       <c r="Q36" t="n">
-        <v>441</v>
+        <v>36</v>
       </c>
       <c r="R36" t="n">
-        <v>1472</v>
+        <v>114</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,12 +3828,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1717534756</t>
+          <t>1988141515</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717534756</t>
+          <t>https://m.place.naver.com/place/1988141515</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3842,29 +3850,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>두루네일</t>
+          <t>포쉬네일 홈플러스킨텍스점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>wngjstodrkr@naver.com</t>
+          <t>lucyjuni@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1328-2941</t>
+          <t>0507-1333-4281</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 119호 두루네일</t>
+          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wngjstodrkr</t>
+          <t>http://www.instagram.com/forsynail_kintex</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3879,7 +3887,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3890,7 +3898,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3899,13 +3907,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="Q37" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="R37" t="n">
-        <v>658</v>
+        <v>532</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,12 +3922,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1944067140</t>
+          <t>1485591782</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944067140</t>
+          <t>https://m.place.naver.com/place/1485591782</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3936,29 +3944,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>기린네일</t>
+          <t>츠키네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>minvl@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1468-7932</t>
+          <t>0507-1328-9708</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kirrin_nail</t>
+          <t>https://www.instagram.com/thuki_nail/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3993,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>115</v>
+        <v>343</v>
       </c>
       <c r="Q38" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>170</v>
+        <v>345</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,12 +4016,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1349667462</t>
+          <t>1363998342</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349667462</t>
+          <t>https://m.place.naver.com/place/1363998342</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4030,29 +4038,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>뮤다네일</t>
+          <t>이제이네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bbakyang@naver.com</t>
+          <t>dmsgml4848@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1389-7130</t>
+          <t>0507-1357-0503</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/myuda_nail/</t>
+          <t>http://www.instagram.com/eeej_nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4087,13 +4095,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="R39" t="n">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,12 +4110,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1129578077</t>
+          <t>37902943</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129578077</t>
+          <t>https://m.place.naver.com/place/37902943</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4124,29 +4132,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일브랜디 일산킨텍스점</t>
+          <t>칙스네일 일산백석점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>chixs_nail@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1325-6774</t>
+          <t>0507-1324-6973</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
+          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_b_randy</t>
+          <t>https://www.instagram.com/chixsnail_</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4181,13 +4189,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>262</v>
+        <v>1185</v>
       </c>
       <c r="Q40" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="R40" t="n">
-        <v>326</v>
+        <v>1272</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,12 +4204,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1125128328</t>
+          <t>1834147957</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125128328</t>
+          <t>https://m.place.naver.com/place/1834147957</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4218,29 +4226,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>네일맑음래쉬</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>yutin60537@naver.com</t>
+          <t>rlazzzzzz@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1463-2316</t>
+          <t>0507-1356-7749</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4266,7 +4274,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4275,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>553</v>
+        <v>37</v>
       </c>
       <c r="Q41" t="n">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="R41" t="n">
-        <v>690</v>
+        <v>46</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,12 +4298,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1105591278</t>
+          <t>1604742986</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105591278</t>
+          <t>https://m.place.naver.com/place/1604742986</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4312,29 +4320,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일스튜디오하몽</t>
+          <t>네일누와</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>laviedekey@naver.com</t>
+          <t>yea0907@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1480-0355</t>
+          <t>0507-1355-6322</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
+          <t>http://pf.kakao.com/_ClIdn/chat</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4369,13 +4377,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>585</v>
+        <v>167</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R42" t="n">
-        <v>609</v>
+        <v>190</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,12 +4392,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1865813904</t>
+          <t>1005319723</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865813904</t>
+          <t>https://m.place.naver.com/place/1005319723</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4406,34 +4414,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아르다뷰티 네일&amp;속눈썹</t>
+          <t>네일 드 제니</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>hja1213@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1354-1704</t>
+          <t>0507-1416-4932</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
+          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_qJhgb</t>
+          <t>https://www.instagram.com/nail_de_jeny</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4463,13 +4471,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,12 +4486,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1958887188</t>
+          <t>1635177150</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958887188</t>
+          <t>https://m.place.naver.com/place/1635177150</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4500,29 +4508,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일앤스타일</t>
+          <t>포쉬네일 뉴코아아울렛일산점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nailnstyle_@naver.com</t>
+          <t>p_yoojin@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1438-5770</t>
+          <t>0507-1486-0212</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
+          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nstyle_lab</t>
+          <t>https://www.instagram.com/forsynail_madu</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4557,13 +4565,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3036</v>
+        <v>489</v>
       </c>
       <c r="Q44" t="n">
-        <v>830</v>
+        <v>123</v>
       </c>
       <c r="R44" t="n">
-        <v>3866</v>
+        <v>612</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4572,12 +4580,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>31424432</t>
+          <t>1089108291</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31424432</t>
+          <t>https://m.place.naver.com/place/1089108291</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4594,29 +4602,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일누와</t>
+          <t>오드네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>astro_sexy@naver.com</t>
+          <t>seong30526@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1355-6322</t>
+          <t>0507-1368-7567</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ClIdn/chat</t>
+          <t>http://pf.kakao.com/_Kfxacn</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4651,13 +4659,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R45" t="n">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4666,12 +4674,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1005319723</t>
+          <t>2026543533</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005319723</t>
+          <t>https://m.place.naver.com/place/2026543533</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4688,48 +4696,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>르네상스</t>
+          <t>별빛네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>suny6668@naver.com</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>support@herren.co.kr</t>
-        </is>
-      </c>
+          <t>naminail@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1406-4890</t>
+          <t>0507-1311-0283</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/166708</t>
+          <t>https://www.instagram.com/_byeolbit_nail/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4740,7 +4744,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4749,13 +4753,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>511</v>
+        <v>252</v>
       </c>
       <c r="Q46" t="n">
-        <v>249</v>
+        <v>11</v>
       </c>
       <c r="R46" t="n">
-        <v>760</v>
+        <v>263</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4764,12 +4768,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>468197702</t>
+          <t>2011766876</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/468197702</t>
+          <t>https://m.place.naver.com/place/2011766876</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4786,29 +4790,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>별빛네일</t>
+          <t>온네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>naminail@naver.com</t>
+          <t>guswnwnwn@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1311-0283</t>
+          <t>0507-1347-5700</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_byeolbit_nail/</t>
+          <t>https://www.instagram.com/onnail__</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4843,13 +4847,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>252</v>
+        <v>1759</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R47" t="n">
-        <v>263</v>
+        <v>1776</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4858,12 +4862,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2011766876</t>
+          <t>31298365</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011766876</t>
+          <t>https://m.place.naver.com/place/31298365</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4880,34 +4884,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>네일로희</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mimisuji52@naver.com</t>
+          <t>younglia_@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1416-6295</t>
+          <t>0507-1349-2502</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 685</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mimisuji52</t>
+          <t>http://pf.kakao.com/_xlXLKn</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4917,7 +4921,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4928,7 +4932,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4937,13 +4941,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="R48" t="n">
-        <v>112</v>
+        <v>312</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4952,12 +4956,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1952745044</t>
+          <t>1049597572</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952745044</t>
+          <t>https://m.place.naver.com/place/1049597572</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4974,29 +4978,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>무이네일</t>
+          <t>네일뮤토</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>baeyou0417@naver.com</t>
+          <t>ithgml123@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1351-6051</t>
+          <t>0507-1370-0857</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
+          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muinail_</t>
+          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5031,13 +5035,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>219</v>
+        <v>10</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5046,12 +5050,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1218582286</t>
+          <t>1260058171</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218582286</t>
+          <t>https://m.place.naver.com/place/1260058171</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5068,29 +5072,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일은뷰티</t>
+          <t>제이 뷰티 클리어</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>topnailjina@naver.com</t>
+          <t>jonghyun0823@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1393-0807</t>
+          <t>0507-1342-8831</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
+          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_eunbeauty</t>
+          <t>https://open.kakao.com/o/sBf6NdCd</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5116,7 +5120,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5125,13 +5129,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>445</v>
+        <v>354</v>
       </c>
       <c r="Q50" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="R50" t="n">
-        <v>549</v>
+        <v>394</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5140,12 +5144,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1421368108</t>
+          <t>1701276497</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421368108</t>
+          <t>https://m.place.naver.com/place/1701276497</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5162,29 +5166,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일뮤토</t>
+          <t>네일 바이 무제</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ithgml123@naver.com</t>
+          <t>a4001a@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1370-0857</t>
+          <t>0507-1330-5463</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
+          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
+          <t>https://www.instagram.com/nails_by_mooze</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5219,13 +5223,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="R51" t="n">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5234,12 +5238,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1260058171</t>
+          <t>1593406269</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260058171</t>
+          <t>https://m.place.naver.com/place/1593406269</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5256,29 +5260,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>물들다, 네일</t>
+          <t>네일바이아르</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>nailbyare@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1472-1621</t>
+          <t>0507-1441-7961</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
+          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nailbyare/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5313,13 +5317,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q52" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5328,12 +5332,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2066663730</t>
+          <t>2094840936</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066663730</t>
+          <t>https://m.place.naver.com/place/2094840936</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5350,34 +5354,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>비온네일 일산킨텍스점</t>
+          <t>주디네일 정발산본점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>feb_7th@naver.com</t>
+          <t>rkflrkfl1@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1384-4180</t>
+          <t>0507-1464-0970</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
+          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HDxnPn</t>
+          <t>https://blog.naver.com/rkflrkfl1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5387,7 +5391,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5398,7 +5402,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5407,13 +5411,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="R53" t="n">
-        <v>114</v>
+        <v>465</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5422,12 +5426,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1988141515</t>
+          <t>1885034449</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1988141515</t>
+          <t>https://m.place.naver.com/place/1885034449</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5444,34 +5448,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일스콘</t>
+          <t>발톱닥터</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>alizee8@naver.com</t>
+          <t>jallana@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1384-0383</t>
+          <t>0507-1409-8838</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sTlxmG</t>
+          <t>https://www.instagram.com/bt_doctor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5492,7 +5496,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5501,13 +5505,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>286</v>
+        <v>155</v>
       </c>
       <c r="Q54" t="n">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="R54" t="n">
-        <v>364</v>
+        <v>479</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5516,12 +5520,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1345185463</t>
+          <t>36651631</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345185463</t>
+          <t>https://m.place.naver.com/place/36651631</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5538,30 +5542,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>어썸네일</t>
+          <t>라미살롱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>loves0226@naver.com</t>
+          <t>marsfive@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1386-1988</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zCyUG/friend</t>
+          <t>https://www.instagram.com/rami_salon88</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5582,7 +5590,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5591,13 +5599,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>68</v>
+        <v>702</v>
       </c>
       <c r="Q55" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="R55" t="n">
-        <v>98</v>
+        <v>763</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5606,12 +5614,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1080419201</t>
+          <t>1314158350</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080419201</t>
+          <t>https://m.place.naver.com/place/1314158350</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5628,39 +5636,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일더무드</t>
+          <t>디엘 네일앤뷰티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2skgus7@naver.com</t>
+          <t>soms0m@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1417-7531</t>
+          <t>0507-1392-5930</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
+          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_bWPiG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5676,22 +5684,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>345</v>
+        <v>87</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="R56" t="n">
-        <v>350</v>
+        <v>151</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5700,12 +5708,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1154624160</t>
+          <t>2001645591</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154624160</t>
+          <t>https://m.place.naver.com/place/2001645591</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5722,29 +5730,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>라미살롱</t>
+          <t>오니뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>marsfive@naver.com</t>
+          <t>onibeauty@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1386-1988</t>
+          <t>0507-1486-0275</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rami_salon88</t>
+          <t>https://www.instagram.com/_onibeauty_/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5779,13 +5787,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>702</v>
+        <v>1031</v>
       </c>
       <c r="Q57" t="n">
-        <v>61</v>
+        <v>441</v>
       </c>
       <c r="R57" t="n">
-        <v>763</v>
+        <v>1472</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5794,12 +5802,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1314158350</t>
+          <t>1717534756</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314158350</t>
+          <t>https://m.place.naver.com/place/1717534756</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5910,24 +5918,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아토네일스튜디오 일산</t>
+          <t>네일오티디</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sesehhh@naver.com</t>
+          <t>swc1439@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1461-2141</t>
+          <t>0507-1429-0763</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
+          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5967,13 +5975,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>925</v>
+        <v>152</v>
       </c>
       <c r="Q59" t="n">
-        <v>542</v>
+        <v>8</v>
       </c>
       <c r="R59" t="n">
-        <v>1467</v>
+        <v>160</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5982,12 +5990,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1419778439</t>
+          <t>2026395486</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419778439</t>
+          <t>https://m.place.naver.com/place/2026395486</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6004,29 +6012,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일바이아르</t>
+          <t>토리네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>nailbyare@naver.com</t>
+          <t>torinail9994@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1441-7961</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyare/</t>
+          <t>http://www.instagram.com/torinail9994</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6061,13 +6065,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>179</v>
       </c>
       <c r="R60" t="n">
-        <v>68</v>
+        <v>203</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6076,12 +6080,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2094840936</t>
+          <t>1327373273</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094840936</t>
+          <t>https://m.place.naver.com/place/1327373273</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6098,29 +6102,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일오티디</t>
+          <t>쏘야네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>swc1439@naver.com</t>
+          <t>dlthdus1541@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1429-0763</t>
+          <t>0507-1377-6460</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dlthdus1541</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6130,12 +6134,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6151,17 +6155,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>152</v>
+        <v>442</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>219</v>
       </c>
       <c r="R61" t="n">
-        <v>160</v>
+        <v>661</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6170,12 +6174,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2026395486</t>
+          <t>1952042243</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026395486</t>
+          <t>https://m.place.naver.com/place/1952042243</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6192,34 +6196,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>반스네일</t>
+          <t>두루네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>white880704@naver.com</t>
+          <t>wngjstodrkr@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1323-9981</t>
+          <t>0507-1328-2941</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 119호 두루네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AXAmn</t>
+          <t>https://blog.naver.com/wngjstodrkr</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6229,7 +6233,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6249,13 +6253,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>67</v>
+        <v>529</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="R62" t="n">
-        <v>76</v>
+        <v>658</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6264,12 +6268,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>612271526</t>
+          <t>1944067140</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/612271526</t>
+          <t>https://m.place.naver.com/place/1944067140</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6286,29 +6290,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jujunail0713@naver.com</t>
+          <t>mimisuji52@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1404-4143</t>
+          <t>0507-1416-6295</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
+          <t>경기도 고양시 일산서구 고양대로 685</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pediheal_ilsan</t>
+          <t>https://blog.naver.com/mimisuji52</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6323,7 +6327,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6343,13 +6347,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="Q63" t="n">
-        <v>276</v>
+        <v>14</v>
       </c>
       <c r="R63" t="n">
-        <v>485</v>
+        <v>112</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6358,12 +6362,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>13092675</t>
+          <t>1952745044</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13092675</t>
+          <t>https://m.place.naver.com/place/1952745044</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6380,29 +6384,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일맑음래쉬</t>
+          <t>레푸스 일산장항점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rlazzzzzz@naver.com</t>
+          <t>yoonaejang@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1356-7749</t>
+          <t>0507-1395-4179</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6417,7 +6421,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6428,22 +6432,22 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>37</v>
+        <v>1923</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>645</v>
       </c>
       <c r="R64" t="n">
-        <v>46</v>
+        <v>2568</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6452,12 +6456,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1604742986</t>
+          <t>90030989</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604742986</t>
+          <t>https://m.place.naver.com/place/90030989</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6474,34 +6478,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오드네일</t>
+          <t>네일은뷰티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>seong30526@naver.com</t>
+          <t>topnailjina@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1368-7567</t>
+          <t>0507-1393-0807</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
+          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Kfxacn</t>
+          <t>https://www.instagram.com/nail_eunbeauty</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6522,7 +6526,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6531,13 +6535,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>62</v>
+        <v>445</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="R65" t="n">
-        <v>78</v>
+        <v>549</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6546,12 +6550,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2026543533</t>
+          <t>1421368108</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026543533</t>
+          <t>https://m.place.naver.com/place/1421368108</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6568,34 +6572,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>소울메이트네일샵</t>
+          <t>네일스튜디오하몽</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>algmlspdlf@naver.com</t>
+          <t>laviedekey@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1382-5531</t>
+          <t>0507-1480-0355</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/soulmatenail</t>
+          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6616,7 +6620,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6625,13 +6629,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>229</v>
+        <v>585</v>
       </c>
       <c r="Q66" t="n">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="R66" t="n">
-        <v>392</v>
+        <v>609</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6640,12 +6644,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>36620432</t>
+          <t>1865813904</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36620432</t>
+          <t>https://m.place.naver.com/place/1865813904</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6662,29 +6666,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일팩토리</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nailfactory13@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1323-3381</t>
+          <t>0507-1385-4858</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https:///linktr.ee/Nail_Factory13</t>
+          <t>https://www.instagram.com/nail_ree_</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6710,7 +6714,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6719,13 +6723,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1023</v>
+        <v>315</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="R67" t="n">
-        <v>1033</v>
+        <v>402</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6734,12 +6738,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1383137709</t>
+          <t>1653728375</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383137709</t>
+          <t>https://m.place.naver.com/place/1653728375</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6756,29 +6760,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>오묘네일</t>
+          <t>허앤밀네일 일산본점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>skme12@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1351-1060</t>
+          <t>0507-1387-0713</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
+          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/5.myo_art</t>
+          <t>https://www.instagram.com/heo_mil_nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6813,13 +6817,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>284</v>
+        <v>1106</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="R68" t="n">
-        <v>313</v>
+        <v>1112</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6828,12 +6832,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1036508811</t>
+          <t>1482502953</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036508811</t>
+          <t>https://m.place.naver.com/place/1482502953</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6850,29 +6854,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>라온네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>yutin60537@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1418-7723</t>
+          <t>0507-1463-2316</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
+          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada._.nail/</t>
+          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6898,7 +6902,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6907,13 +6911,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>81</v>
+        <v>553</v>
       </c>
       <c r="Q69" t="n">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="R69" t="n">
-        <v>103</v>
+        <v>690</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6922,12 +6926,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1226786349</t>
+          <t>1105591278</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226786349</t>
+          <t>https://m.place.naver.com/place/1105591278</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6944,29 +6948,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>운디아네일</t>
+          <t>마이유네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>undia10@naver.com</t>
+          <t>tasha81@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1327-8629</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
+          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/undia_nail</t>
+          <t>https://www.instagram.com/my_u_nail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7001,13 +7001,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1823</v>
+        <v>63</v>
       </c>
       <c r="Q70" t="n">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>1989</v>
+        <v>65</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7016,12 +7016,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1192977296</t>
+          <t>2037646051</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192977296</t>
+          <t>https://m.place.naver.com/place/2037646051</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7038,29 +7038,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>주디네일 정발산본점</t>
+          <t>소울메이트네일샵</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>rkflrkfl1@naver.com</t>
+          <t>algmlspdlf@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1464-0970</t>
+          <t>0507-1382-5531</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkflrkfl1</t>
+          <t>http://www.instagram.com/soulmatenail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7095,13 +7095,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>444</v>
+        <v>229</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="R71" t="n">
-        <v>465</v>
+        <v>392</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1885034449</t>
+          <t>36620432</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885034449</t>
+          <t>https://m.place.naver.com/place/36620432</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7132,29 +7132,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>바이마이네일</t>
+          <t>네일무아</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jjeong_1004_@naver.com</t>
+          <t>loowowool@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1303-0274</t>
+          <t>0507-1322-4700</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymynail_</t>
+          <t>https://www.instagram.com/nail_mua_</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7189,13 +7189,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="Q72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1712300996</t>
+          <t>2028306533</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712300996</t>
+          <t>https://m.place.naver.com/place/2028306533</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7226,29 +7226,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>제이 뷰티 클리어</t>
+          <t>오묘네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jonghyun0823@naver.com</t>
+          <t>skme12@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1342-8831</t>
+          <t>0507-1351-1060</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
+          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBf6NdCd</t>
+          <t>http://www.instagram.com/5.myo_art</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7274,7 +7274,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="Q73" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="R73" t="n">
-        <v>394</v>
+        <v>313</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7298,12 +7298,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1701276497</t>
+          <t>1036508811</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701276497</t>
+          <t>https://m.place.naver.com/place/1036508811</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7320,29 +7320,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>츠키네일</t>
+          <t>무이네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>minvl@naver.com</t>
+          <t>baeyou0417@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1328-9708</t>
+          <t>0507-1351-6051</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thuki_nail/</t>
+          <t>https://www.instagram.com/muinail_</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>343</v>
+        <v>219</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>345</v>
+        <v>222</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,12 +7392,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1363998342</t>
+          <t>1218582286</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363998342</t>
+          <t>https://m.place.naver.com/place/1218582286</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>그리심네일&amp;뷰티</t>
+          <t>홀리네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>herb2592@naver.com</t>
+          <t>ko3hi@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1329-7483</t>
+          <t>0507-1353-4205</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/herb2592</t>
+          <t>https://www.instagram.com/holy._.nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7471,13 +7471,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="Q75" t="n">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="R75" t="n">
-        <v>350</v>
+        <v>433</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7486,12 +7486,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1667004401</t>
+          <t>37849636</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667004401</t>
+          <t>https://m.place.naver.com/place/37849636</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7508,29 +7508,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
+          <t>뮤트뷰티</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>garinh_56@naver.com</t>
+          <t>mute_e@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>031-815-3435</t>
+          <t>0507-1410-0371</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://instagram.com/salondeluce_</t>
+          <t>https://blog.naver.com/mute_e</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7565,13 +7565,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>427</v>
+        <v>218</v>
       </c>
       <c r="Q76" t="n">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="R76" t="n">
-        <v>515</v>
+        <v>233</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1385267282</t>
+          <t>1641314586</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1385267282</t>
+          <t>https://m.place.naver.com/place/1641314586</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_nail/일산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/일산_네일샵.xlsx
@@ -564,34 +564,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>조조네일</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>pulin0114@naver.com</t>
-        </is>
-      </c>
+          <t>네일디어원</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1307-3090</t>
+          <t>0507-1417-4781</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jojonail.official</t>
+          <t>https://pf.kakao.com/_xlCxgxbG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +608,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="R2" t="n">
-        <v>62</v>
+        <v>971</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1911173276</t>
+          <t>1054380281</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911173276</t>
+          <t>https://m.place.naver.com/place/1054380281</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>W네일</t>
+          <t>더블앤뷰티 레푸스 일산주엽점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>w-nail@naver.com</t>
+          <t>x7x7x7love@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1436-9888</t>
+          <t>0507-1337-3327</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 14-4 2층</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/wnail1543/</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>124</v>
+        <v>422</v>
       </c>
       <c r="Q3" t="n">
-        <v>99</v>
+        <v>388</v>
       </c>
       <c r="R3" t="n">
-        <v>223</v>
+        <v>810</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37842153</t>
+          <t>1209456950</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37842153</t>
+          <t>https://m.place.naver.com/place/1209456950</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,30 +748,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>어썸네일</t>
+          <t>칙스네일 일산백석점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>loves0226@naver.com</t>
+          <t>chixs_nail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1324-6973</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zCyUG/friend</t>
+          <t>https://www.instagram.com/chixsnail_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>68</v>
+        <v>1189</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="R4" t="n">
-        <v>98</v>
+        <v>1283</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1080419201</t>
+          <t>1834147957</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080419201</t>
+          <t>https://m.place.naver.com/place/1834147957</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -842,25 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>렐라네일</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cinderellais@naver.com</t>
-        </is>
-      </c>
+          <t>네일뮤토</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1370-0857</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
+          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rella_nail</t>
+          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1949626855</t>
+          <t>1260058171</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949626855</t>
+          <t>https://m.place.naver.com/place/1260058171</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바이마이네일</t>
+          <t>주디네일 정발산본점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jjeong_1004_@naver.com</t>
+          <t>rkflrkfl1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1303-0274</t>
+          <t>0507-1464-0970</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
+          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymynail_</t>
+          <t>https://blog.naver.com/rkflrkfl1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>191</v>
+        <v>444</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>196</v>
+        <v>465</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1712300996</t>
+          <t>1885034449</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712300996</t>
+          <t>https://m.place.naver.com/place/1885034449</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1026,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>youngnail0121@naver.com</t>
+          <t>garinh_56@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1411-7300</t>
+          <t>031-815-3435</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
+          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youngnail0121</t>
+          <t>http://instagram.com/salondeluce_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>788</v>
+        <v>427</v>
       </c>
       <c r="Q7" t="n">
-        <v>287</v>
+        <v>88</v>
       </c>
       <c r="R7" t="n">
-        <v>1075</v>
+        <v>515</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13464862</t>
+          <t>1385267282</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13464862</t>
+          <t>https://m.place.naver.com/place/1385267282</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>운디아네일</t>
+          <t>오오비 네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>undia10@naver.com</t>
+          <t>dltmdgus1206@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1327-8629</t>
+          <t>0507-1332-3495</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
+          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/undia_nail</t>
+          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1823</v>
+        <v>61</v>
       </c>
       <c r="Q8" t="n">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1989</v>
+        <v>75</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1192977296</t>
+          <t>2008508308</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192977296</t>
+          <t>https://m.place.naver.com/place/2008508308</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1214,34 +1214,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일더무드</t>
+          <t>그리심네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2skgus7@naver.com</t>
+          <t>herb2592@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1417-7531</t>
+          <t>0507-1329-7483</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
+          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_bWPiG</t>
+          <t>https://blog.naver.com/herb2592</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1262,7 +1262,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>345</v>
+        <v>258</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="R9" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1154624160</t>
+          <t>1667004401</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154624160</t>
+          <t>https://m.place.naver.com/place/1667004401</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>물들다, 네일</t>
+          <t>라온네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>yutin60537@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1472-1621</t>
+          <t>0507-1463-2316</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
+          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>55</v>
+        <v>553</v>
       </c>
       <c r="Q10" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="R10" t="n">
-        <v>111</v>
+        <v>690</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2066663730</t>
+          <t>1105591278</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066663730</t>
+          <t>https://m.place.naver.com/place/1105591278</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1402,34 +1402,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
+          <t>네일스콘</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jujunail0713@naver.com</t>
+          <t>alizee8@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1404-4143</t>
+          <t>0507-1384-0383</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
+          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pediheal_ilsan</t>
+          <t>http://pf.kakao.com/_sTlxmG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1450,7 +1450,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="Q11" t="n">
-        <v>276</v>
+        <v>78</v>
       </c>
       <c r="R11" t="n">
-        <v>485</v>
+        <v>364</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13092675</t>
+          <t>1345185463</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13092675</t>
+          <t>https://m.place.naver.com/place/1345185463</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라망네일</t>
+          <t>두루네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ehyeon4862@naver.com</t>
+          <t>wngjstodrkr@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1409-8266</t>
+          <t>0507-1328-2941</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 119호 두루네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://instagram.com/lamain_naily</t>
+          <t>https://blog.naver.com/wngjstodrkr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1544,7 +1544,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>259</v>
+        <v>529</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="R12" t="n">
-        <v>265</v>
+        <v>658</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1819287959</t>
+          <t>1944067140</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819287959</t>
+          <t>https://m.place.naver.com/place/1944067140</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1590,39 +1590,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아토네일스튜디오 일산</t>
+          <t>네일로희</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sesehhh@naver.com</t>
+          <t>younglia_@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1461-2141</t>
+          <t>0507-1349-2502</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xlXLKn</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1638,22 +1638,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>925</v>
+        <v>255</v>
       </c>
       <c r="Q13" t="n">
-        <v>542</v>
+        <v>57</v>
       </c>
       <c r="R13" t="n">
-        <v>1467</v>
+        <v>312</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1419778439</t>
+          <t>1049597572</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419778439</t>
+          <t>https://m.place.naver.com/place/1049597572</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기린네일</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>mimisuji52@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1468-7932</t>
+          <t>0507-1416-6295</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
+          <t>경기도 고양시 일산서구 고양대로 685</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kirrin_nail</t>
+          <t>https://blog.naver.com/mimisuji52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="Q14" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1349667462</t>
+          <t>1952745044</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349667462</t>
+          <t>https://m.place.naver.com/place/1952745044</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1778,34 +1778,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일르엘</t>
+          <t>온네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>apoco123@naver.com</t>
+          <t>guswnwnwn@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1371-6033</t>
+          <t>0507-1347-5700</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaLFXG/chat</t>
+          <t>https://www.instagram.com/onnail__</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1826,7 +1826,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>308</v>
+        <v>1759</v>
       </c>
       <c r="Q15" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="R15" t="n">
-        <v>359</v>
+        <v>1776</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1006093671</t>
+          <t>31298365</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006093671</t>
+          <t>https://m.place.naver.com/place/31298365</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1872,34 +1872,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일리쉬</t>
+          <t>제제샵</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>moonnsleep@naver.com</t>
+          <t>rowjddms2@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1384-3764</t>
+          <t>0507-1395-0132</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
+          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_CRNHxd</t>
+          <t>http://www.instagram.com/all.beauty_jeje</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1920,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>242</v>
+        <v>367</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="R16" t="n">
-        <v>272</v>
+        <v>451</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1946279327</t>
+          <t>1262615516</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946279327</t>
+          <t>https://m.place.naver.com/place/1262615516</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1966,39 +1966,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>리아네일</t>
+          <t>네일, 또 놀자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ryddltptkd1401@naver.com</t>
+          <t>ji-berry@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1356-7914</t>
+          <t>0507-1377-6207</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크로 113 아이파크 1단지 상가동 201호</t>
+          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYe5QWRPu</t>
+          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2014,7 +2014,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>163</v>
+        <v>388</v>
       </c>
       <c r="Q17" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="R17" t="n">
-        <v>235</v>
+        <v>415</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1188570648</t>
+          <t>1416423106</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188570648</t>
+          <t>https://m.place.naver.com/place/1416423106</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>더블앤뷰티 레푸스 일산주엽점</t>
+          <t>네일누와</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>x7x7x7love@naver.com</t>
+          <t>yea0907@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1337-3327</t>
+          <t>0507-1355-6322</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>http://pf.kakao.com/_ClIdn/chat</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>422</v>
+        <v>167</v>
       </c>
       <c r="Q18" t="n">
-        <v>388</v>
+        <v>23</v>
       </c>
       <c r="R18" t="n">
-        <v>810</v>
+        <v>190</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1209456950</t>
+          <t>1005319723</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209456950</t>
+          <t>https://m.place.naver.com/place/1005319723</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2154,34 +2154,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>오오비 네일</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>dltmdgus1206@naver.com</t>
-        </is>
-      </c>
+          <t>반스네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1332-3495</t>
+          <t>0507-1323-9981</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
+          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
+          <t>http://pf.kakao.com/_AXAmn</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2202,7 +2198,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2211,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2008508308</t>
+          <t>612271526</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2008508308</t>
+          <t>https://m.place.naver.com/place/612271526</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2248,34 +2244,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>뮤다네일</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>bbakyang@naver.com</t>
-        </is>
-      </c>
+          <t>어썸네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1389-7130</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
+          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/myuda_nail/</t>
+          <t>http://pf.kakao.com/_zCyUG/friend</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2296,7 +2284,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2305,13 +2293,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>285</v>
+        <v>68</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
-        <v>290</v>
+        <v>98</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2308,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1129578077</t>
+          <t>1080419201</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129578077</t>
+          <t>https://m.place.naver.com/place/1080419201</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2342,39 +2330,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일, 또 놀자</t>
+          <t>리아네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dmsquf7541@naver.com</t>
+          <t>ryddltptkd1401@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1377-6207</t>
+          <t>0507-1356-7914</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
+          <t>경기도 고양시 일산서구 하이파크로 113 아이파크 1단지 상가동 201호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
+          <t>https://toss.place/_lb/TYe5QWRPu</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2390,7 +2378,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2399,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>388</v>
+        <v>163</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="R21" t="n">
-        <v>415</v>
+        <v>235</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2402,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1416423106</t>
+          <t>1188570648</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1416423106</t>
+          <t>https://m.place.naver.com/place/1188570648</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2436,34 +2424,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일스콘</t>
+          <t>물들다, 네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>alizee8@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1384-0383</t>
+          <t>0507-1472-1621</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
+          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sTlxmG</t>
+          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2484,7 +2472,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2493,13 +2481,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>286</v>
+        <v>55</v>
       </c>
       <c r="Q22" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="R22" t="n">
-        <v>364</v>
+        <v>112</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2496,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1345185463</t>
+          <t>2066663730</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345185463</t>
+          <t>https://m.place.naver.com/place/2066663730</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2518,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
+          <t>네일 드 제니</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>garinh_56@naver.com</t>
+          <t>hja1213@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>031-815-3435</t>
+          <t>0507-1416-4932</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
+          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://instagram.com/salondeluce_</t>
+          <t>https://www.instagram.com/nail_de_jeny</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2578,7 +2566,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2587,13 +2575,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>427</v>
+        <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>515</v>
+        <v>152</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2590,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1385267282</t>
+          <t>1635177150</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1385267282</t>
+          <t>https://m.place.naver.com/place/1635177150</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2624,34 +2612,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일_하니</t>
+          <t>발톱닥터</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lunefronde@naver.com</t>
+          <t>jallana@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1490-1526</t>
+          <t>0507-1409-8838</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnDQmn/chat</t>
+          <t>https://www.instagram.com/bt_doctor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2672,7 +2660,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="Q24" t="n">
-        <v>71</v>
+        <v>324</v>
       </c>
       <c r="R24" t="n">
-        <v>274</v>
+        <v>479</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2076477973</t>
+          <t>36651631</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076477973</t>
+          <t>https://m.place.naver.com/place/36651631</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2706,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>그리심네일&amp;뷰티</t>
+          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>herb2592@naver.com</t>
+          <t>jujunail0713@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1329-7483</t>
+          <t>0507-1404-4143</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/herb2592</t>
+          <t>https://www.instagram.com/pediheal_ilsan</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2755,7 +2743,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2775,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="Q25" t="n">
-        <v>91</v>
+        <v>276</v>
       </c>
       <c r="R25" t="n">
-        <v>350</v>
+        <v>486</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1667004401</t>
+          <t>13092675</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667004401</t>
+          <t>https://m.place.naver.com/place/13092675</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일,숩</t>
+          <t>포쉬네일 뉴코아아울렛일산점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hyunjju1541@naver.com</t>
+          <t>p_yoojin@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1325-8243</t>
+          <t>0507-1486-0212</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
+          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___soop</t>
+          <t>https://www.instagram.com/forsynail_madu</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,13 +2857,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>146</v>
+        <v>489</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="R26" t="n">
-        <v>151</v>
+        <v>612</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2872,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1126898433</t>
+          <t>1089108291</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126898433</t>
+          <t>https://m.place.naver.com/place/1089108291</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2906,34 +2894,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일앤스타일</t>
+          <t>네일스튜디오하몽</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nailnstyle_@naver.com</t>
+          <t>laviedekey@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1438-5770</t>
+          <t>0507-1480-0355</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nstyle_lab</t>
+          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2954,7 +2942,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2963,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3036</v>
+        <v>585</v>
       </c>
       <c r="Q27" t="n">
-        <v>830</v>
+        <v>24</v>
       </c>
       <c r="R27" t="n">
-        <v>3866</v>
+        <v>609</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>31424432</t>
+          <t>1865813904</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31424432</t>
+          <t>https://m.place.naver.com/place/1865813904</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3000,48 +2988,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>르네상스</t>
+          <t>조조네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>suny6668@naver.com</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>support@herren.co.kr</t>
-        </is>
-      </c>
+          <t>pulin0114@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1406-4890</t>
+          <t>0507-1307-3090</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
+          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/166708</t>
+          <t>https://www.instagram.com/jojonail.official</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3052,7 +3036,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3061,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>511</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="n">
-        <v>249</v>
+        <v>16</v>
       </c>
       <c r="R28" t="n">
-        <v>760</v>
+        <v>62</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,17 +3060,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>468197702</t>
+          <t>1911173276</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/468197702</t>
+          <t>https://m.place.naver.com/place/1911173276</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3098,34 +3082,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아르다뷰티 네일&amp;속눈썹</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1354-1704</t>
+          <t>0507-1385-4858</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_qJhgb</t>
+          <t>https://www.instagram.com/nail_ree_</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3146,7 +3130,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3155,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>169</v>
+        <v>315</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="R29" t="n">
-        <v>178</v>
+        <v>402</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3154,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1958887188</t>
+          <t>1653728375</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958887188</t>
+          <t>https://m.place.naver.com/place/1653728375</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3192,34 +3176,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일브랜디 일산킨텍스점</t>
+          <t>네일리쉬</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>moonnsleep@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1325-6774</t>
+          <t>0507-1384-3764</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_b_randy</t>
+          <t>http://pf.kakao.com/_CRNHxd</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3240,7 +3224,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3249,13 +3233,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="Q30" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="R30" t="n">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,17 +3248,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1125128328</t>
+          <t>1946279327</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125128328</t>
+          <t>https://m.place.naver.com/place/1946279327</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3286,34 +3270,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일팩토리</t>
+          <t>비온네일 일산킨텍스점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nailfactory13@naver.com</t>
+          <t>feb_7th@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1323-3381</t>
+          <t>0507-1384-4180</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https:///linktr.ee/Nail_Factory13</t>
+          <t>http://pf.kakao.com/_HDxnPn</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3343,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1023</v>
+        <v>78</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="R31" t="n">
-        <v>1033</v>
+        <v>114</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,17 +3342,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1383137709</t>
+          <t>1988141515</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383137709</t>
+          <t>https://m.place.naver.com/place/1988141515</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3380,34 +3364,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>반스네일</t>
+          <t>라망네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>white880704@naver.com</t>
+          <t>ehyeon4862@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1323-9981</t>
+          <t>0507-1409-8266</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
+          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AXAmn</t>
+          <t>https://instagram.com/lamain_naily</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3428,7 +3412,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3437,13 +3421,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>67</v>
+        <v>259</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>76</v>
+        <v>265</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,17 +3436,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>612271526</t>
+          <t>1819287959</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/612271526</t>
+          <t>https://m.place.naver.com/place/1819287959</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3474,29 +3458,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S뷰티네일 일산주엽점</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>s-beauty06@naver.com</t>
+          <t>youngnail0121@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1327-9513</t>
+          <t>0507-1411-7300</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s-beauty06</t>
+          <t>https://www.instagram.com/youngnail0121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,7 +3495,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3527,17 +3511,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>478</v>
+        <v>788</v>
       </c>
       <c r="Q33" t="n">
-        <v>426</v>
+        <v>287</v>
       </c>
       <c r="R33" t="n">
-        <v>904</v>
+        <v>1075</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3546,17 +3530,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1247940545</t>
+          <t>13464862</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247940545</t>
+          <t>https://m.place.naver.com/place/13464862</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3568,34 +3552,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일디어원</t>
+          <t>네일 바이 무제</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>eee2sia@naver.com</t>
+          <t>su28min5054@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1417-4781</t>
+          <t>0507-1330-5463</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
+          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlCxgxbG</t>
+          <t>https://www.instagram.com/nails_by_mooze</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3616,7 +3600,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3625,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>897</v>
+        <v>55</v>
       </c>
       <c r="Q34" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R34" t="n">
-        <v>968</v>
+        <v>128</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3640,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1054380281</t>
+          <t>1593406269</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054380281</t>
+          <t>https://m.place.naver.com/place/1593406269</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3662,34 +3646,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>네일_하니</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>lunefronde@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1418-7723</t>
+          <t>0507-1490-1526</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada._.nail/</t>
+          <t>http://pf.kakao.com/_xnDQmn/chat</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3710,7 +3694,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3719,13 +3703,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="R35" t="n">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1226786349</t>
+          <t>2076477973</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226786349</t>
+          <t>https://m.place.naver.com/place/2076477973</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3756,34 +3740,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>비온네일 일산킨텍스점</t>
+          <t>쏘야네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb_7th@naver.com</t>
+          <t>dlthdus1541@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1384-4180</t>
+          <t>0507-1377-6460</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HDxnPn</t>
+          <t>https://blog.naver.com/dlthdus1541</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3793,7 +3777,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3804,7 +3788,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3813,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>219</v>
       </c>
       <c r="R36" t="n">
-        <v>114</v>
+        <v>661</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3828,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1988141515</t>
+          <t>1952042243</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1988141515</t>
+          <t>https://m.place.naver.com/place/1952042243</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3850,29 +3834,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>포쉬네일 홈플러스킨텍스점</t>
+          <t>라미살롱</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>lucyjuni@naver.com</t>
+          <t>marsfive@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1333-4281</t>
+          <t>0507-1386-1988</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/forsynail_kintex</t>
+          <t>https://www.instagram.com/rami_salon88</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3907,13 +3891,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>463</v>
+        <v>701</v>
       </c>
       <c r="Q37" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="R37" t="n">
-        <v>532</v>
+        <v>762</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3922,17 +3906,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1485591782</t>
+          <t>1314158350</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485591782</t>
+          <t>https://m.place.naver.com/place/1314158350</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3944,29 +3928,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>츠키네일</t>
+          <t>토리네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>minvl@naver.com</t>
+          <t>torinail9994@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1328-9708</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thuki_nail/</t>
+          <t>http://www.instagram.com/torinail9994</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4001,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>343</v>
+        <v>24</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="R38" t="n">
-        <v>345</v>
+        <v>203</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4016,17 +3996,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1363998342</t>
+          <t>1327373273</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363998342</t>
+          <t>https://m.place.naver.com/place/1327373273</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4038,29 +4018,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이제이네일</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>dmsgml4848@naver.com</t>
-        </is>
-      </c>
+          <t>디엘 네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1357-0503</t>
+          <t>0507-1392-5930</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
+          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/eeej_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4070,7 +4046,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4091,17 +4067,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>327</v>
+        <v>87</v>
       </c>
       <c r="Q39" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="R39" t="n">
-        <v>357</v>
+        <v>152</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4110,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>37902943</t>
+          <t>2001645591</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37902943</t>
+          <t>https://m.place.naver.com/place/2001645591</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4132,34 +4108,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>칙스네일 일산백석점</t>
+          <t>네일더무드</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>chixs_nail@naver.com</t>
+          <t>2skgus7@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1324-6973</t>
+          <t>0507-1417-7531</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
+          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chixsnail_</t>
+          <t>https://pf.kakao.com/_bWPiG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4180,7 +4156,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4189,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1185</v>
+        <v>343</v>
       </c>
       <c r="Q40" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>1272</v>
+        <v>348</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4204,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1834147957</t>
+          <t>1154624160</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834147957</t>
+          <t>https://m.place.naver.com/place/1154624160</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4226,29 +4202,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일맑음래쉬</t>
+          <t>W네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>rlazzzzzz@naver.com</t>
+          <t>w-nail@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1356-7749</t>
+          <t>0507-1436-9888</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 14-4 2층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/wnail1543/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4283,13 +4259,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="R41" t="n">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4298,17 +4274,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1604742986</t>
+          <t>37842153</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604742986</t>
+          <t>https://m.place.naver.com/place/37842153</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4320,39 +4296,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일누와</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>yea0907@naver.com</t>
-        </is>
-      </c>
+          <t>아토네일스튜디오 일산</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1355-6322</t>
+          <t>0507-1461-2141</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
+          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ClIdn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4368,22 +4340,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>167</v>
+        <v>925</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>542</v>
       </c>
       <c r="R42" t="n">
-        <v>190</v>
+        <v>1467</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4392,17 +4364,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1005319723</t>
+          <t>1419778439</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005319723</t>
+          <t>https://m.place.naver.com/place/1419778439</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4414,29 +4386,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일 드 제니</t>
+          <t>무이네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hja1213@naver.com</t>
+          <t>baeyou0417@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1416-4932</t>
+          <t>0507-1351-6051</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_jeny</t>
+          <t>https://www.instagram.com/muinail_</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4462,7 +4434,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4471,13 +4443,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4486,17 +4458,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1635177150</t>
+          <t>1218582286</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1635177150</t>
+          <t>https://m.place.naver.com/place/1218582286</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4508,34 +4480,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>포쉬네일 뉴코아아울렛일산점</t>
+          <t>오드네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>p_yoojin@naver.com</t>
+          <t>seong30526@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1486-0212</t>
+          <t>0507-1368-7567</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_madu</t>
+          <t>http://pf.kakao.com/_Kfxacn</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4556,7 +4528,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4565,13 +4537,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>489</v>
+        <v>62</v>
       </c>
       <c r="Q44" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="R44" t="n">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4580,17 +4552,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1089108291</t>
+          <t>2026543533</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089108291</t>
+          <t>https://m.place.naver.com/place/2026543533</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4602,34 +4574,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>오드네일</t>
+          <t>운디아네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>seong30526@naver.com</t>
+          <t>undia10@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1368-7567</t>
+          <t>0507-1327-8629</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
+          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Kfxacn</t>
+          <t>http://www.instagram.com/undia_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4650,7 +4622,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4659,13 +4631,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>62</v>
+        <v>1822</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="R45" t="n">
-        <v>78</v>
+        <v>1988</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4674,17 +4646,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026543533</t>
+          <t>1192977296</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026543533</t>
+          <t>https://m.place.naver.com/place/1192977296</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4696,29 +4668,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>별빛네일</t>
+          <t>뮤트뷰티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>naminail@naver.com</t>
+          <t>mute_e@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1311-0283</t>
+          <t>0507-1410-0371</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_byeolbit_nail/</t>
+          <t>https://blog.naver.com/mute_e</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4733,7 +4705,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4753,13 +4725,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4768,17 +4740,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2011766876</t>
+          <t>1641314586</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011766876</t>
+          <t>https://m.place.naver.com/place/1641314586</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4790,29 +4762,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>온네일</t>
+          <t>이제이네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>guswnwnwn@naver.com</t>
+          <t>dmsgml4848@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1347-5700</t>
+          <t>0507-1357-0503</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onnail__</t>
+          <t>http://www.instagram.com/eeej_nail</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4847,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1759</v>
+        <v>327</v>
       </c>
       <c r="Q47" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="R47" t="n">
-        <v>1776</v>
+        <v>357</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4862,17 +4834,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>31298365</t>
+          <t>37902943</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31298365</t>
+          <t>https://m.place.naver.com/place/37902943</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4884,34 +4856,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일로희</t>
+          <t>오니뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>younglia_@naver.com</t>
+          <t>onibeauty@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1349-2502</t>
+          <t>0507-1486-0275</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlXLKn</t>
+          <t>https://www.instagram.com/_onibeauty_/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4932,7 +4904,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4941,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>255</v>
+        <v>1032</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>441</v>
       </c>
       <c r="R48" t="n">
-        <v>312</v>
+        <v>1473</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4956,17 +4928,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1049597572</t>
+          <t>1717534756</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049597572</t>
+          <t>https://m.place.naver.com/place/1717534756</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4978,29 +4950,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일뮤토</t>
+          <t>렐라네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ithgml123@naver.com</t>
+          <t>cinderellais@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1370-0857</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
+          <t>https://www.instagram.com/rella_nail</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5035,13 +5003,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5050,17 +5018,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1260058171</t>
+          <t>1949626855</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260058171</t>
+          <t>https://m.place.naver.com/place/1949626855</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5072,29 +5040,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>제이 뷰티 클리어</t>
+          <t>허앤밀네일 일산본점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jonghyun0823@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1342-8831</t>
+          <t>0507-1387-0713</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
+          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBf6NdCd</t>
+          <t>https://www.instagram.com/heo_mil_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5120,7 +5088,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5129,13 +5097,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>354</v>
+        <v>1107</v>
       </c>
       <c r="Q50" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>394</v>
+        <v>1113</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5144,17 +5112,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1701276497</t>
+          <t>1482502953</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701276497</t>
+          <t>https://m.place.naver.com/place/1482502953</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5166,44 +5134,48 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일 바이 무제</t>
+          <t>르네상스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>a4001a@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>suny6668@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>support@herren.co.kr</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1330-5463</t>
+          <t>0507-1406-4890</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nails_by_mooze</t>
+          <t>https://booking.naver.com/booking/13/bizes/166708</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5214,7 +5186,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5223,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>55</v>
+        <v>512</v>
       </c>
       <c r="Q51" t="n">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="R51" t="n">
-        <v>128</v>
+        <v>761</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5238,17 +5210,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1593406269</t>
+          <t>468197702</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593406269</t>
+          <t>https://m.place.naver.com/place/468197702</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5260,34 +5232,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일바이아르</t>
+          <t>아르다뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nailbyare@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1441-7961</t>
+          <t>0507-1354-1704</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyare/</t>
+          <t>https://pf.kakao.com/_qJhgb</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5308,7 +5280,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5317,13 +5289,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R52" t="n">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5332,17 +5304,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2094840936</t>
+          <t>1958887188</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094840936</t>
+          <t>https://m.place.naver.com/place/1958887188</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5354,29 +5326,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>주디네일 정발산본점</t>
+          <t>홀리네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rkflrkfl1@naver.com</t>
+          <t>ko3hi@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1464-0970</t>
+          <t>0507-1353-4205</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkflrkfl1</t>
+          <t>https://www.instagram.com/holy._.nail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5391,7 +5363,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5411,13 +5383,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>444</v>
+        <v>227</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="R53" t="n">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5426,17 +5398,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1885034449</t>
+          <t>37849636</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885034449</t>
+          <t>https://m.place.naver.com/place/37849636</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5448,29 +5420,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>발톱닥터</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>jallana@naver.com</t>
-        </is>
-      </c>
+          <t>네일브랜디 일산킨텍스점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1409-8838</t>
+          <t>0507-1325-6774</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bt_doctor</t>
+          <t>https://www.instagram.com/nail_b_randy</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5505,13 +5473,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="Q54" t="n">
-        <v>324</v>
+        <v>64</v>
       </c>
       <c r="R54" t="n">
-        <v>479</v>
+        <v>326</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5520,17 +5488,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>36651631</t>
+          <t>1125128328</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36651631</t>
+          <t>https://m.place.naver.com/place/1125128328</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5542,29 +5510,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>라미살롱</t>
+          <t>네일오티디</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>marsfive@naver.com</t>
+          <t>yoorrimchang@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1386-1988</t>
+          <t>0507-1429-0763</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
+          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rami_salon88</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5574,7 +5542,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5595,17 +5563,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>702</v>
+        <v>152</v>
       </c>
       <c r="Q55" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="R55" t="n">
-        <v>763</v>
+        <v>161</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5614,17 +5582,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1314158350</t>
+          <t>2026395486</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314158350</t>
+          <t>https://m.place.naver.com/place/2026395486</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5636,29 +5604,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>디엘 네일앤뷰티</t>
+          <t>제이 뷰티 클리어</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>soms0m@naver.com</t>
+          <t>jonghyun0823@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1392-5930</t>
+          <t>0507-1342-8831</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
+          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sBf6NdCd</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5668,7 +5636,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5684,22 +5652,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>87</v>
+        <v>354</v>
       </c>
       <c r="Q56" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="R56" t="n">
-        <v>151</v>
+        <v>394</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5708,17 +5676,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2001645591</t>
+          <t>1701276497</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001645591</t>
+          <t>https://m.place.naver.com/place/1701276497</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5730,29 +5698,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오니뷰티 네일&amp;속눈썹</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>onibeauty@naver.com</t>
-        </is>
-      </c>
+          <t>오묘네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1486-0275</t>
+          <t>0507-1351-1060</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
+          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onibeauty_/</t>
+          <t>http://www.instagram.com/5.myo_art</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5787,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1031</v>
+        <v>284</v>
       </c>
       <c r="Q57" t="n">
-        <v>441</v>
+        <v>29</v>
       </c>
       <c r="R57" t="n">
-        <v>1472</v>
+        <v>313</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5802,17 +5766,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1717534756</t>
+          <t>1036508811</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717534756</t>
+          <t>https://m.place.naver.com/place/1036508811</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5824,29 +5788,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>제제샵</t>
+          <t>네일바이아르</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>rowjddms2@naver.com</t>
+          <t>nailbyare@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1395-0132</t>
+          <t>0507-1441-7961</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
+          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/all.beauty_jeje</t>
+          <t>https://www.instagram.com/nailbyare/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5881,13 +5845,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>367</v>
+        <v>64</v>
       </c>
       <c r="Q58" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>451</v>
+        <v>69</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5896,17 +5860,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1262615516</t>
+          <t>2094840936</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262615516</t>
+          <t>https://m.place.naver.com/place/2094840936</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5918,39 +5882,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일오티디</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>swc1439@naver.com</t>
-        </is>
-      </c>
+          <t>네일르엘</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1429-0763</t>
+          <t>0507-1371-6033</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xaLFXG/chat</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5966,22 +5926,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>152</v>
+        <v>309</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="R59" t="n">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5990,17 +5950,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026395486</t>
+          <t>1006093671</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026395486</t>
+          <t>https://m.place.naver.com/place/1006093671</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6012,25 +5972,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>토리네일</t>
+          <t>네일앤스타일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>torinail9994@naver.com</t>
+          <t>nailnstyle_@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1438-5770</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/torinail9994</t>
+          <t>https://www.instagram.com/nstyle_lab</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6065,13 +6029,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>3038</v>
       </c>
       <c r="Q60" t="n">
-        <v>179</v>
+        <v>830</v>
       </c>
       <c r="R60" t="n">
-        <v>203</v>
+        <v>3868</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6080,17 +6044,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1327373273</t>
+          <t>31424432</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327373273</t>
+          <t>https://m.place.naver.com/place/31424432</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6102,29 +6066,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>쏘야네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>dlthdus1541@naver.com</t>
-        </is>
-      </c>
+          <t>네일,숩</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1377-6460</t>
+          <t>0507-1325-8243</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
+          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlthdus1541</t>
+          <t>https://www.instagram.com/nail___soop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,7 +6099,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6159,13 +6119,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>442</v>
+        <v>146</v>
       </c>
       <c r="Q61" t="n">
-        <v>219</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>661</v>
+        <v>151</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6174,17 +6134,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1952042243</t>
+          <t>1126898433</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952042243</t>
+          <t>https://m.place.naver.com/place/1126898433</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6196,29 +6156,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>두루네일</t>
+          <t>별빛네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>wngjstodrkr@naver.com</t>
+          <t>naminail@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1328-2941</t>
+          <t>0507-1311-0283</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 119호 두루네일</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wngjstodrkr</t>
+          <t>https://www.instagram.com/_byeolbit_nail/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6233,7 +6193,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6244,7 +6204,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6253,13 +6213,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>529</v>
+        <v>252</v>
       </c>
       <c r="Q62" t="n">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="R62" t="n">
-        <v>658</v>
+        <v>263</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6268,17 +6228,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1944067140</t>
+          <t>2011766876</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944067140</t>
+          <t>https://m.place.naver.com/place/2011766876</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6290,29 +6250,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mimisuji52@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1416-6295</t>
+          <t>0507-1418-7723</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 685</t>
+          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mimisuji52</t>
+          <t>https://www.instagram.com/dada._.nail/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6327,7 +6287,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6347,13 +6307,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="Q63" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="R63" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6362,17 +6322,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1952745044</t>
+          <t>1226786349</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952745044</t>
+          <t>https://m.place.naver.com/place/1226786349</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6384,29 +6344,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>레푸스 일산장항점</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>yoonaejang@naver.com</t>
-        </is>
-      </c>
+          <t>네일맑음래쉬</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1395-4179</t>
+          <t>0507-1356-7749</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
+          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6421,7 +6377,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6432,22 +6388,22 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1923</v>
+        <v>37</v>
       </c>
       <c r="Q64" t="n">
-        <v>645</v>
+        <v>9</v>
       </c>
       <c r="R64" t="n">
-        <v>2568</v>
+        <v>46</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6456,17 +6412,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>90030989</t>
+          <t>1604742986</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/90030989</t>
+          <t>https://m.place.naver.com/place/1604742986</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6478,29 +6434,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일은뷰티</t>
+          <t>츠키네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>topnailjina@naver.com</t>
+          <t>minvl@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1393-0807</t>
+          <t>0507-1328-9708</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
+          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_eunbeauty</t>
+          <t>https://www.instagram.com/thuki_nail/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6535,13 +6491,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>445</v>
+        <v>343</v>
       </c>
       <c r="Q65" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>549</v>
+        <v>345</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6550,17 +6506,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1421368108</t>
+          <t>1363998342</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421368108</t>
+          <t>https://m.place.naver.com/place/1363998342</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6572,34 +6528,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일스튜디오하몽</t>
+          <t>네일무아</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>laviedekey@naver.com</t>
+          <t>loowowool@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1480-0355</t>
+          <t>0507-1322-4700</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
+          <t>https://www.instagram.com/nail_mua_</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6620,7 +6576,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6629,13 +6585,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>585</v>
+        <v>92</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>609</v>
+        <v>92</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6644,17 +6600,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1865813904</t>
+          <t>2028306533</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865813904</t>
+          <t>https://m.place.naver.com/place/2028306533</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6666,29 +6622,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>네일팩토리</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>nailfactory13@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1385-4858</t>
+          <t>0507-1323-3381</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ree_</t>
+          <t>https:///linktr.ee/Nail_Factory13</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6714,7 +6670,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6723,13 +6679,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>315</v>
+        <v>1023</v>
       </c>
       <c r="Q67" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="R67" t="n">
-        <v>402</v>
+        <v>1033</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6738,17 +6694,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1653728375</t>
+          <t>1383137709</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653728375</t>
+          <t>https://m.place.naver.com/place/1383137709</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6760,29 +6716,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>허앤밀네일 일산본점</t>
+          <t>레푸스 일산장항점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>yoonaejang@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1387-0713</t>
+          <t>0507-1395-4179</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heo_mil_nail</t>
+          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6797,7 +6753,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6808,22 +6764,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1106</v>
+        <v>1922</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>645</v>
       </c>
       <c r="R68" t="n">
-        <v>1112</v>
+        <v>2567</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6832,17 +6788,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1482502953</t>
+          <t>90030989</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482502953</t>
+          <t>https://m.place.naver.com/place/90030989</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6854,29 +6810,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>기린네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yutin60537@naver.com</t>
+          <t>ssso131@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1463-2316</t>
+          <t>0507-1468-7932</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>https://www.instagram.com/kirrin_nail</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6902,7 +6858,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6911,13 +6867,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>553</v>
+        <v>115</v>
       </c>
       <c r="Q69" t="n">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="R69" t="n">
-        <v>690</v>
+        <v>170</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6926,17 +6882,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1105591278</t>
+          <t>1349667462</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105591278</t>
+          <t>https://m.place.naver.com/place/1349667462</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6948,25 +6904,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>마이유네일</t>
+          <t>바이마이네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>tasha81@naver.com</t>
+          <t>jjeong_1004_@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1303-0274</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
+          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/my_u_nail</t>
+          <t>https://www.instagram.com/bymynail_</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7001,13 +6961,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7016,17 +6976,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2037646051</t>
+          <t>1712300996</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037646051</t>
+          <t>https://m.place.naver.com/place/1712300996</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7038,29 +6998,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>소울메이트네일샵</t>
+          <t>S뷰티네일 일산주엽점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>algmlspdlf@naver.com</t>
+          <t>s-beauty06@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1382-5531</t>
+          <t>0507-1327-9513</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/soulmatenail</t>
+          <t>https://blog.naver.com/s-beauty06</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7075,7 +7035,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7091,17 +7051,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>229</v>
+        <v>478</v>
       </c>
       <c r="Q71" t="n">
-        <v>163</v>
+        <v>426</v>
       </c>
       <c r="R71" t="n">
-        <v>392</v>
+        <v>904</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7110,17 +7070,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>36620432</t>
+          <t>1247940545</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36620432</t>
+          <t>https://m.place.naver.com/place/1247940545</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7132,29 +7092,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일무아</t>
+          <t>소울메이트네일샵</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>algmlspdlf@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1322-4700</t>
+          <t>0507-1382-5531</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mua_</t>
+          <t>http://www.instagram.com/soulmatenail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7189,13 +7149,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="R72" t="n">
-        <v>90</v>
+        <v>392</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7204,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2028306533</t>
+          <t>36620432</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028306533</t>
+          <t>https://m.place.naver.com/place/36620432</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7226,29 +7186,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오묘네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>skme12@naver.com</t>
-        </is>
-      </c>
+          <t>뮤다네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1351-1060</t>
+          <t>0507-1389-7130</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/5.myo_art</t>
+          <t>https://www.instagram.com/myuda_nail/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7283,13 +7239,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q73" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="R73" t="n">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7298,17 +7254,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1036508811</t>
+          <t>1129578077</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036508811</t>
+          <t>https://m.place.naver.com/place/1129578077</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7320,29 +7276,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>무이네일</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>baeyou0417@naver.com</t>
-        </is>
-      </c>
+          <t>포쉬네일 홈플러스킨텍스점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1351-6051</t>
+          <t>0507-1333-4281</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
+          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muinail_</t>
+          <t>http://www.instagram.com/forsynail_kintex</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7377,13 +7329,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>219</v>
+        <v>463</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="R74" t="n">
-        <v>222</v>
+        <v>532</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,17 +7344,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1218582286</t>
+          <t>1485591782</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218582286</t>
+          <t>https://m.place.naver.com/place/1485591782</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7414,29 +7366,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>홀리네일</t>
+          <t>네일은뷰티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ko3hi@naver.com</t>
+          <t>topnailjina@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1353-4205</t>
+          <t>0507-1393-0807</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
+          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/holy._.nail</t>
+          <t>https://www.instagram.com/nail_eunbeauty</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7471,13 +7423,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>227</v>
+        <v>445</v>
       </c>
       <c r="Q75" t="n">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="R75" t="n">
-        <v>433</v>
+        <v>549</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7486,17 +7438,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>37849636</t>
+          <t>1421368108</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37849636</t>
+          <t>https://m.place.naver.com/place/1421368108</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7508,29 +7460,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>뮤트뷰티</t>
+          <t>마이유네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mute_e@naver.com</t>
+          <t>tasha81@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1410-0371</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
+          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mute_e</t>
+          <t>https://www.instagram.com/my_u_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7545,7 +7493,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7565,13 +7513,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="Q76" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7580,17 +7528,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1641314586</t>
+          <t>2037646051</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641314586</t>
+          <t>https://m.place.naver.com/place/2037646051</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/일산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/일산_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일디어원</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>네일르엘</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>apoco123@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1417-4781</t>
+          <t>0507-1371-6033</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlCxgxbG</t>
+          <t>http://pf.kakao.com/_xaLFXG/chat</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>900</v>
+        <v>311</v>
       </c>
       <c r="Q2" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="R2" t="n">
-        <v>971</v>
+        <v>363</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1054380281</t>
+          <t>1006093671</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054380281</t>
+          <t>https://m.place.naver.com/place/1006093671</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -654,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더블앤뷰티 레푸스 일산주엽점</t>
+          <t>제제샵</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x7x7x7love@naver.com</t>
+          <t>rowjddms2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1337-3327</t>
+          <t>0507-1395-0132</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
+          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>http://www.instagram.com/all.beauty_jeje</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>422</v>
+        <v>367</v>
       </c>
       <c r="Q3" t="n">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="R3" t="n">
-        <v>810</v>
+        <v>450</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1209456950</t>
+          <t>1262615516</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209456950</t>
+          <t>https://m.place.naver.com/place/1262615516</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>칙스네일 일산백석점</t>
+          <t>다다네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chixs_nail@naver.com</t>
+          <t>tykd2048@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1324-6973</t>
+          <t>0507-1418-7723</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
+          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chixsnail_</t>
+          <t>https://www.instagram.com/dada._.nail/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1189</v>
+        <v>81</v>
       </c>
       <c r="Q4" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="R4" t="n">
-        <v>1283</v>
+        <v>103</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1834147957</t>
+          <t>1226786349</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834147957</t>
+          <t>https://m.place.naver.com/place/1226786349</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,25 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일뮤토</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>씬네일</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>soha9892@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1370-0857</t>
+          <t>0507-1359-1074</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
+          <t>경기도 고양시 일산동구 숲속마을2로 176 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
+          <t>https://www.instagram.com/_ssin.nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1260058171</t>
+          <t>1453894916</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260058171</t>
+          <t>https://m.place.naver.com/place/1453894916</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -932,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>주디네일 정발산본점</t>
+          <t>햄찌네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rkflrkfl1@naver.com</t>
+          <t>hyde_1969@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1464-0970</t>
+          <t>0507-1470-4647</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 130호 햄찌네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkflrkfl1</t>
+          <t>https://open.kakao.com/o/sBRrKmFf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -969,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -980,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1885034449</t>
+          <t>1157803048</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885034449</t>
+          <t>https://m.place.naver.com/place/1157803048</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
+          <t>이제이네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>garinh_56@naver.com</t>
+          <t>seul3024@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-815-3435</t>
+          <t>0507-1357-0503</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/salondeluce_</t>
+          <t>http://www.instagram.com/eeej_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>427</v>
+        <v>327</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>515</v>
+        <v>357</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1385267282</t>
+          <t>37902943</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1385267282</t>
+          <t>https://m.place.naver.com/place/37902943</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오오비 네일</t>
+          <t>레푸스 일산장항점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dltmdgus1206@naver.com</t>
+          <t>yoonaejang@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1332-3495</t>
+          <t>0507-1395-4179</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
+          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1168,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>61</v>
+        <v>1922</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>645</v>
       </c>
       <c r="R8" t="n">
-        <v>75</v>
+        <v>2567</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2008508308</t>
+          <t>90030989</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2008508308</t>
+          <t>https://m.place.naver.com/place/90030989</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그리심네일&amp;뷰티</t>
+          <t>뮤다네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>herb2592@naver.com</t>
+          <t>bbakyang@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1329-7483</t>
+          <t>0507-1389-7130</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/herb2592</t>
+          <t>https://www.instagram.com/myuda_nail/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="Q9" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>349</v>
+        <v>290</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1667004401</t>
+          <t>1129578077</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667004401</t>
+          <t>https://m.place.naver.com/place/1129578077</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>라망네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yutin60537@naver.com</t>
+          <t>ehyeon4862@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1463-2316</t>
+          <t>0507-1409-8266</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
+          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
+          <t>https://instagram.com/lamain_naily</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>553</v>
+        <v>259</v>
       </c>
       <c r="Q10" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>690</v>
+        <v>265</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1105591278</t>
+          <t>1819287959</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105591278</t>
+          <t>https://m.place.naver.com/place/1819287959</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1402,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일스콘</t>
+          <t>뮤트뷰티</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>alizee8@naver.com</t>
+          <t>mute_e@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1384-0383</t>
+          <t>0507-1410-0371</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sTlxmG</t>
+          <t>https://blog.naver.com/mute_e</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1439,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1450,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="Q11" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
-        <v>364</v>
+        <v>236</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1345185463</t>
+          <t>1641314586</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1345185463</t>
+          <t>https://m.place.naver.com/place/1641314586</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>두루네일</t>
+          <t>네일맑음래쉬</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wngjstodrkr@naver.com</t>
+          <t>rlazzzzzz@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1328-2941</t>
+          <t>0507-1356-7749</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 119호 두루네일</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wngjstodrkr</t>
+          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1533,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1544,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1553,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>529</v>
+        <v>37</v>
       </c>
       <c r="Q12" t="n">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>658</v>
+        <v>46</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1944067140</t>
+          <t>1604742986</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944067140</t>
+          <t>https://m.place.naver.com/place/1604742986</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1590,34 +1598,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일로희</t>
+          <t>칙스네일 일산백석점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>younglia_@naver.com</t>
+          <t>chixs_nail@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1349-2502</t>
+          <t>0507-1324-6973</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
+          <t>경기도 고양시 일산동구 중앙로 1079 백석역 더리브스타일 1층 106호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlXLKn</t>
+          <t>https://www.instagram.com/chixsnail_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1638,7 +1646,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>255</v>
+        <v>1195</v>
       </c>
       <c r="Q13" t="n">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="R13" t="n">
-        <v>312</v>
+        <v>1296</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1049597572</t>
+          <t>1834147957</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049597572</t>
+          <t>https://m.place.naver.com/place/1834147957</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>포쉬네일 뉴코아아울렛일산점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mimisuji52@naver.com</t>
+          <t>p_yoojin@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1416-6295</t>
+          <t>0507-1486-0212</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 685</t>
+          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mimisuji52</t>
+          <t>https://www.instagram.com/forsynail_madu</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>98</v>
+        <v>489</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="R14" t="n">
-        <v>112</v>
+        <v>612</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1952745044</t>
+          <t>1089108291</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952745044</t>
+          <t>https://m.place.naver.com/place/1089108291</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>온네일</t>
+          <t>오니뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>guswnwnwn@naver.com</t>
+          <t>onibeauty@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1347-5700</t>
+          <t>0507-1486-0275</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onnail__</t>
+          <t>https://www.instagram.com/_onibeauty_/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1835,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1759</v>
+        <v>1034</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>443</v>
       </c>
       <c r="R15" t="n">
-        <v>1776</v>
+        <v>1477</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1858,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>31298365</t>
+          <t>1717534756</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31298365</t>
+          <t>https://m.place.naver.com/place/1717534756</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1880,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>제제샵</t>
+          <t>허앤밀네일 일산본점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rowjddms2@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1395-0132</t>
+          <t>0507-1387-0713</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 2층 203호</t>
+          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/all.beauty_jeje</t>
+          <t>https://www.instagram.com/heo_mil_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1929,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>367</v>
+        <v>1110</v>
       </c>
       <c r="Q16" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>451</v>
+        <v>1116</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1952,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1262615516</t>
+          <t>1482502953</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262615516</t>
+          <t>https://m.place.naver.com/place/1482502953</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1974,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일, 또 놀자</t>
+          <t>살롱드루체 네일 속눈썹 일산 킨텍스 본점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ji-berry@naver.com</t>
+          <t>garinh_56@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1377-6207</t>
+          <t>031-815-3435</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 217-23 더샵그라비스타 상가동 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
+          <t>http://instagram.com/salondeluce_</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2023,13 +2031,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R17" t="n">
-        <v>415</v>
+        <v>514</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2046,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1416423106</t>
+          <t>1385267282</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1416423106</t>
+          <t>https://m.place.naver.com/place/1385267282</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2060,34 +2068,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일누와</t>
+          <t>소울메이트네일샵</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yea0907@naver.com</t>
+          <t>algmlspdlf@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1355-6322</t>
+          <t>0507-1382-5531</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ClIdn/chat</t>
+          <t>http://www.instagram.com/soulmatenail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2108,7 +2116,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="R18" t="n">
-        <v>190</v>
+        <v>392</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2140,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1005319723</t>
+          <t>36620432</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005319723</t>
+          <t>https://m.place.naver.com/place/36620432</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2154,30 +2162,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>반스네일</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>포쉬네일 홈플러스킨텍스점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lucyjuni@naver.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1323-9981</t>
+          <t>0507-1333-4281</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
+          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AXAmn</t>
+          <t>http://www.instagram.com/forsynail_kintex</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2198,7 +2210,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2207,13 +2219,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>67</v>
+        <v>463</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="R19" t="n">
-        <v>76</v>
+        <v>532</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2234,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>612271526</t>
+          <t>1485591782</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/612271526</t>
+          <t>https://m.place.naver.com/place/1485591782</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2244,26 +2256,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>어썸네일</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>홀리네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>miho6677@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1353-4205</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zCyUG/friend</t>
+          <t>https://www.instagram.com/holy._.nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2284,7 +2304,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2293,13 +2313,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>68</v>
+        <v>227</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="R20" t="n">
-        <v>98</v>
+        <v>433</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2308,17 +2328,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1080419201</t>
+          <t>37849636</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080419201</t>
+          <t>https://m.place.naver.com/place/37849636</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2330,29 +2350,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>리아네일</t>
+          <t>반스네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ryddltptkd1401@naver.com</t>
+          <t>white880704@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1356-7914</t>
+          <t>0507-1323-9981</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크로 113 아이파크 1단지 상가동 201호</t>
+          <t>경기도 고양시 일산동구 일산로441번길 15-2 반스네일</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYe5QWRPu</t>
+          <t>http://pf.kakao.com/_AXAmn</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2362,7 +2382,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2387,13 +2407,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="Q21" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>235</v>
+        <v>76</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2402,17 +2422,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1188570648</t>
+          <t>612271526</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188570648</t>
+          <t>https://m.place.naver.com/place/612271526</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2424,44 +2444,48 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>물들다, 네일</t>
+          <t>르네상스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>suny6668@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>support@herren.co.kr</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1472-1621</t>
+          <t>0507-1406-4890</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
+          <t>https://booking.naver.com/booking/13/bizes/166708</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2472,7 +2496,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2481,13 +2505,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>55</v>
+        <v>512</v>
       </c>
       <c r="Q22" t="n">
-        <v>57</v>
+        <v>249</v>
       </c>
       <c r="R22" t="n">
-        <v>112</v>
+        <v>761</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2496,17 +2520,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2066663730</t>
+          <t>468197702</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066663730</t>
+          <t>https://m.place.naver.com/place/468197702</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2518,29 +2542,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일 드 제니</t>
+          <t>별빛네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hja1213@naver.com</t>
+          <t>naminail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1416-4932</t>
+          <t>0507-1311-0283</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_jeny</t>
+          <t>https://www.instagram.com/_byeolbit_nail/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,7 +2590,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2575,13 +2599,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R23" t="n">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2590,17 +2614,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1635177150</t>
+          <t>2011766876</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1635177150</t>
+          <t>https://m.place.naver.com/place/2011766876</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2612,29 +2636,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>발톱닥터</t>
+          <t>운디아네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jallana@naver.com</t>
+          <t>undia10@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1409-8838</t>
+          <t>0507-1327-8629</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
+          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bt_doctor</t>
+          <t>http://www.instagram.com/undia_nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2669,13 +2693,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>155</v>
+        <v>1824</v>
       </c>
       <c r="Q24" t="n">
-        <v>324</v>
+        <v>166</v>
       </c>
       <c r="R24" t="n">
-        <v>479</v>
+        <v>1990</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2708,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36651631</t>
+          <t>1192977296</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36651631</t>
+          <t>https://m.place.naver.com/place/1192977296</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2706,34 +2730,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
+          <t>네일더무드</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jujunail0713@naver.com</t>
+          <t>2skgus7@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1404-4143</t>
+          <t>0507-1417-7531</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
+          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pediheal_ilsan</t>
+          <t>https://pf.kakao.com/_bWPiG</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2754,7 +2778,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2763,13 +2787,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>210</v>
+        <v>343</v>
       </c>
       <c r="Q25" t="n">
-        <v>276</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>486</v>
+        <v>348</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2778,17 +2802,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13092675</t>
+          <t>1154624160</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13092675</t>
+          <t>https://m.place.naver.com/place/1154624160</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2800,29 +2824,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>포쉬네일 뉴코아아울렛일산점</t>
+          <t>마이유네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>p_yoojin@naver.com</t>
+          <t>tasha81@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1486-0212</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
+          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_madu</t>
+          <t>https://www.instagram.com/my_u_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,13 +2877,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>489</v>
+        <v>63</v>
       </c>
       <c r="Q26" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>612</v>
+        <v>65</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2892,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1089108291</t>
+          <t>2037646051</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089108291</t>
+          <t>https://m.place.naver.com/place/2037646051</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2894,29 +2914,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일스튜디오하몽</t>
+          <t>네일스콘</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>laviedekey@naver.com</t>
+          <t>alizee8@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1480-0355</t>
+          <t>0507-1384-0383</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
+          <t>경기도 고양시 일산동구 강송로74번길 25 1층 100호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
+          <t>http://pf.kakao.com/_sTlxmG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2951,13 +2971,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>585</v>
+        <v>286</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="R27" t="n">
-        <v>609</v>
+        <v>364</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2966,17 +2986,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1865813904</t>
+          <t>1345185463</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865813904</t>
+          <t>https://m.place.naver.com/place/1345185463</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2988,29 +3008,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>조조네일</t>
+          <t>오묘네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pulin0114@naver.com</t>
+          <t>skme12@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1307-3090</t>
+          <t>0507-1351-1060</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jojonail.official</t>
+          <t>http://www.instagram.com/5.myo_art</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3045,13 +3065,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>46</v>
+        <v>285</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="R28" t="n">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3060,17 +3080,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1911173276</t>
+          <t>1036508811</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911173276</t>
+          <t>https://m.place.naver.com/place/1036508811</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3082,29 +3102,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>네일팩토리</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>nailfactory13@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1385-4858</t>
+          <t>0507-1323-3381</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ree_</t>
+          <t>https:///linktr.ee/Nail_Factory13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3130,7 +3150,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3139,13 +3159,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>315</v>
+        <v>1022</v>
       </c>
       <c r="Q29" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="R29" t="n">
-        <v>402</v>
+        <v>1032</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3174,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1653728375</t>
+          <t>1383137709</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653728375</t>
+          <t>https://m.place.naver.com/place/1383137709</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3196,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일리쉬</t>
+          <t>네일_하니</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>moonnsleep@naver.com</t>
+          <t>lunefronde@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1384-3764</t>
+          <t>0507-1490-1526</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_CRNHxd</t>
+          <t>http://pf.kakao.com/_xnDQmn/chat</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3233,13 +3253,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="R30" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,17 +3268,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1946279327</t>
+          <t>2076477973</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946279327</t>
+          <t>https://m.place.naver.com/place/2076477973</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3270,34 +3290,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비온네일 일산킨텍스점</t>
+          <t>네일은뷰티</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb_7th@naver.com</t>
+          <t>topnailjina@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1384-4180</t>
+          <t>0507-1393-0807</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
+          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HDxnPn</t>
+          <t>https://www.instagram.com/nail_eunbeauty</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3318,7 +3338,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3327,13 +3347,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="R31" t="n">
-        <v>114</v>
+        <v>548</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,17 +3362,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1988141515</t>
+          <t>1421368108</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1988141515</t>
+          <t>https://m.place.naver.com/place/1421368108</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3364,29 +3384,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>라망네일</t>
+          <t>네일,숩</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ehyeon4862@naver.com</t>
+          <t>hyunjju1541@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1409-8266</t>
+          <t>0507-1325-8243</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2차 4층</t>
+          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://instagram.com/lamain_naily</t>
+          <t>https://www.instagram.com/nail___soop</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3421,13 +3441,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3436,17 +3456,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1819287959</t>
+          <t>1126898433</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819287959</t>
+          <t>https://m.place.naver.com/place/1126898433</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3458,29 +3478,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>네일바이아르</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>youngnail0121@naver.com</t>
+          <t>nailbyare@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1411-7300</t>
+          <t>0507-1441-7961</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
+          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youngnail0121</t>
+          <t>https://www.instagram.com/nailbyare/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,13 +3535,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>788</v>
+        <v>64</v>
       </c>
       <c r="Q33" t="n">
-        <v>287</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1075</v>
+        <v>69</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,17 +3550,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>13464862</t>
+          <t>2094840936</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13464862</t>
+          <t>https://m.place.naver.com/place/2094840936</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3552,29 +3572,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일 바이 무제</t>
+          <t>쏘야네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>su28min5054@naver.com</t>
+          <t>dlthdus1541@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1330-5463</t>
+          <t>0507-1377-6460</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
+          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nails_by_mooze</t>
+          <t>https://blog.naver.com/dlthdus1541</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3589,7 +3609,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3609,13 +3629,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>55</v>
+        <v>442</v>
       </c>
       <c r="Q34" t="n">
-        <v>73</v>
+        <v>219</v>
       </c>
       <c r="R34" t="n">
-        <v>128</v>
+        <v>661</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3644,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1593406269</t>
+          <t>1952042243</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593406269</t>
+          <t>https://m.place.naver.com/place/1952042243</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3646,29 +3666,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일_하니</t>
+          <t>네일누와</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>lunefronde@naver.com</t>
+          <t>astro_sexy@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1490-1526</t>
+          <t>0507-1355-6322</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-18 하임빌로데오 211호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 404호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnDQmn/chat</t>
+          <t>http://pf.kakao.com/_ClIdn/chat</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3703,13 +3723,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="Q35" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="R35" t="n">
-        <v>274</v>
+        <v>190</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,17 +3738,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2076477973</t>
+          <t>1005319723</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076477973</t>
+          <t>https://m.place.naver.com/place/1005319723</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3740,29 +3760,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>쏘야네일</t>
+          <t>물들다, 네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dlthdus1541@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1377-6460</t>
+          <t>0507-1472-1621</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 하늘마을1로 2 4층 403호</t>
+          <t>경기도 고양시 일산동구 호수로430번길 30-14 1층 일부</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlthdus1541</t>
+          <t>https://www.instagram.com/muldleda_nail?igsh=MW1sbTM5NXluc2QwbA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3777,7 +3797,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3797,13 +3817,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>442</v>
+        <v>55</v>
       </c>
       <c r="Q36" t="n">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="R36" t="n">
-        <v>661</v>
+        <v>112</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,17 +3832,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1952042243</t>
+          <t>2066663730</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952042243</t>
+          <t>https://m.place.naver.com/place/2066663730</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3834,29 +3854,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>라미살롱</t>
+          <t>네일, 또 놀자</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>marsfive@naver.com</t>
+          <t>ji-berry@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1386-1988</t>
+          <t>0507-1377-6207</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
+          <t>경기도 고양시 일산동구 숲속마을2로 137 상가동 1층 102호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rami_salon88</t>
+          <t>https://www.instagram.com/nail_nolza?igsh=eGowdWc2cXhyMnZz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3891,13 +3911,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>701</v>
+        <v>388</v>
       </c>
       <c r="Q37" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="R37" t="n">
-        <v>762</v>
+        <v>415</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,17 +3926,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1314158350</t>
+          <t>1416423106</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314158350</t>
+          <t>https://m.place.naver.com/place/1416423106</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3948,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>토리네일</t>
+          <t>네일린</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>torinail9994@naver.com</t>
+          <t>cookyismylife@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3941,12 +3961,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 303호</t>
+          <t>경기도 고양시 일산동구 중앙로 1322 일산현대아이스페이스 1층 네일린</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/torinail9994</t>
+          <t>https://www.instagram.com/_nailin___?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3981,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="Q38" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +4016,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1327373273</t>
+          <t>1548509718</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327373273</t>
+          <t>https://m.place.naver.com/place/1548509718</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4018,25 +4038,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>디엘 네일앤뷰티</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ysbfly@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1392-5930</t>
+          <t>0507-1385-4858</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강촌로 118 상가동 1층 103호</t>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 1층 114호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_ree_</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4046,7 +4070,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4067,17 +4091,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q39" t="n">
         <v>87</v>
       </c>
-      <c r="Q39" t="n">
-        <v>65</v>
-      </c>
       <c r="R39" t="n">
-        <v>152</v>
+        <v>402</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,17 +4110,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2001645591</t>
+          <t>1653728375</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001645591</t>
+          <t>https://m.place.naver.com/place/1653728375</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4132,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일더무드</t>
+          <t>네일앤스타일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2skgus7@naver.com</t>
+          <t>nailnstyle_@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1417-7531</t>
+          <t>0507-1438-5770</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주화로 40 동주오피스텔 2층202-2호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_bWPiG</t>
+          <t>https://www.instagram.com/nstyle_lab</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4156,7 +4180,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4165,13 +4189,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>343</v>
+        <v>3037</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>831</v>
       </c>
       <c r="R40" t="n">
-        <v>348</v>
+        <v>3868</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4204,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1154624160</t>
+          <t>31424432</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154624160</t>
+          <t>https://m.place.naver.com/place/31424432</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4202,29 +4226,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>W네일</t>
+          <t>라미살롱</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>w-nail@naver.com</t>
+          <t>marsfive@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1436-9888</t>
+          <t>0507-1386-1988</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 14-4 2층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 3층 308호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/wnail1543/</t>
+          <t>https://www.instagram.com/rami_salon88</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4259,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>124</v>
+        <v>701</v>
       </c>
       <c r="Q41" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="R41" t="n">
-        <v>223</v>
+        <v>762</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,17 +4298,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>37842153</t>
+          <t>1314158350</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37842153</t>
+          <t>https://m.place.naver.com/place/1314158350</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4296,25 +4320,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아토네일스튜디오 일산</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>온네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>guswnwnwn@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1461-2141</t>
+          <t>0507-1347-5700</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔B동 1층 113호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/onnail__</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4324,7 +4352,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4345,17 +4373,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>925</v>
+        <v>1763</v>
       </c>
       <c r="Q42" t="n">
-        <v>542</v>
+        <v>17</v>
       </c>
       <c r="R42" t="n">
-        <v>1467</v>
+        <v>1780</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,17 +4392,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1419778439</t>
+          <t>31298365</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419778439</t>
+          <t>https://m.place.naver.com/place/31298365</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4386,29 +4414,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>무이네일</t>
+          <t>W네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>baeyou0417@naver.com</t>
+          <t>w-nail@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1351-6051</t>
+          <t>0507-1436-9888</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 14-4 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muinail_</t>
+          <t>http://www.instagram.com/wnail1543/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4443,13 +4471,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="R43" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,17 +4486,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1218582286</t>
+          <t>37842153</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218582286</t>
+          <t>https://m.place.naver.com/place/37842153</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4480,34 +4508,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오드네일</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>seong30526@naver.com</t>
+          <t>mimisuji52@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1368-7567</t>
+          <t>0507-1416-6295</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
+          <t>경기도 고양시 일산서구 고양대로 685</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Kfxacn</t>
+          <t>https://blog.naver.com/mimisuji52</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4517,7 +4545,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4528,7 +4556,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4537,13 +4565,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R44" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,17 +4580,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026543533</t>
+          <t>1952745044</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026543533</t>
+          <t>https://m.place.naver.com/place/1952745044</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4574,29 +4602,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>운디아네일</t>
+          <t>기린네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>undia10@naver.com</t>
+          <t>ssso131@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1327-8629</t>
+          <t>0507-1468-7932</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1004번길 33 월드타워 8차 2층 206호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/undia_nail</t>
+          <t>https://www.instagram.com/kirrin_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4631,13 +4659,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1822</v>
+        <v>115</v>
       </c>
       <c r="Q45" t="n">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="R45" t="n">
-        <v>1988</v>
+        <v>170</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,17 +4674,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1192977296</t>
+          <t>1349667462</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192977296</t>
+          <t>https://m.place.naver.com/place/1349667462</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4668,29 +4696,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>뮤트뷰티</t>
+          <t>네일오티디</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mute_e@naver.com</t>
+          <t>yoorrimchang@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1410-0371</t>
+          <t>0507-1429-0763</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 오피스텔 617호</t>
+          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mute_e</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4700,12 +4728,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4721,17 +4749,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R46" t="n">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4768,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1641314586</t>
+          <t>2026395486</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641314586</t>
+          <t>https://m.place.naver.com/place/2026395486</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4762,34 +4790,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>이제이네일</t>
+          <t>네일로희</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dmsgml4848@naver.com</t>
+          <t>younglia_@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1357-0503</t>
+          <t>0507-1349-2502</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 오피스텔 204호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 326호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/eeej_nail</t>
+          <t>http://pf.kakao.com/_xlXLKn</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4810,7 +4838,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4819,13 +4847,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>327</v>
+        <v>256</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="R47" t="n">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4862,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>37902943</t>
+          <t>1049597572</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37902943</t>
+          <t>https://m.place.naver.com/place/1049597572</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4856,34 +4884,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오니뷰티 네일&amp;속눈썹</t>
+          <t>오드네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>onibeauty@naver.com</t>
+          <t>seong30526@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1486-0275</t>
+          <t>0507-1368-7567</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정씨티프라자3 404호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 a동 1층 에이-143호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onibeauty_/</t>
+          <t>http://pf.kakao.com/_Kfxacn</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4904,7 +4932,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4913,13 +4941,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1032</v>
+        <v>62</v>
       </c>
       <c r="Q48" t="n">
-        <v>441</v>
+        <v>16</v>
       </c>
       <c r="R48" t="n">
-        <v>1473</v>
+        <v>78</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,17 +4956,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1717534756</t>
+          <t>2026543533</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717534756</t>
+          <t>https://m.place.naver.com/place/2026543533</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4950,25 +4978,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>렐라네일</t>
+          <t>조조네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>cinderellais@naver.com</t>
+          <t>pulin0114@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1307-3090</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
+          <t>경기도 고양시 일산동구 일산로330번길 39 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rella_nail</t>
+          <t>https://www.instagram.com/jojonail.official</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5003,13 +5035,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R49" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,17 +5050,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1949626855</t>
+          <t>1911173276</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949626855</t>
+          <t>https://m.place.naver.com/place/1911173276</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5040,34 +5072,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>허앤밀네일 일산본점</t>
+          <t>어썸네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>loves0226@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1387-0713</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 2층 203-1호</t>
+          <t>경기도 고양시 일산서구 가좌3로 19 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heo_mil_nail</t>
+          <t>http://pf.kakao.com/_zCyUG/friend</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5088,7 +5116,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5097,13 +5125,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1107</v>
+        <v>68</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R50" t="n">
-        <v>1113</v>
+        <v>98</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5112,17 +5140,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1482502953</t>
+          <t>1080419201</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482502953</t>
+          <t>https://m.place.naver.com/place/1080419201</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5134,48 +5162,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>르네상스</t>
+          <t>오오비 네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>suny6668@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>support@herren.co.kr</t>
-        </is>
-      </c>
+          <t>dltmdgus1206@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1406-4890</t>
+          <t>0507-1332-3495</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 401.403호</t>
+          <t>경기도 고양시 일산동구 백마로 223 현대에뜨레보 3층 336호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/166708</t>
+          <t>https://www.instagram.com/oob_nail?igsh=NGsyYjd1dG8yOGRk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5186,7 +5210,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5195,13 +5219,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>512</v>
+        <v>65</v>
       </c>
       <c r="Q51" t="n">
-        <v>249</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>761</v>
+        <v>79</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,17 +5234,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>468197702</t>
+          <t>2008508308</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/468197702</t>
+          <t>https://m.place.naver.com/place/2008508308</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5232,29 +5256,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>아르다뷰티 네일&amp;속눈썹</t>
+          <t>더블앤뷰티 레푸스 일산주엽점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>x7x7x7love@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1354-1704</t>
+          <t>0507-1337-3327</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크쇼핑타운 3층 S-09호 레푸스</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_qJhgb</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5289,13 +5313,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>388</v>
       </c>
       <c r="R52" t="n">
-        <v>178</v>
+        <v>811</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5328,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1958887188</t>
+          <t>1209456950</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958887188</t>
+          <t>https://m.place.naver.com/place/1209456950</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5326,29 +5350,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>홀리네일</t>
+          <t>네일 라미엔느</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ko3hi@naver.com</t>
+          <t>hawaii_jk@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1353-4205</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 221호 홀리네일</t>
+          <t>경기도 고양시 일산동구 중앙로 1079 더리브스타일 2층 216호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/holy._.nail</t>
+          <t>http://instagram.com/nail_lamienne</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5383,13 +5403,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q53" t="n">
-        <v>206</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>433</v>
+        <v>234</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5398,17 +5418,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>37849636</t>
+          <t>1018192486</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37849636</t>
+          <t>https://m.place.naver.com/place/1018192486</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5420,25 +5440,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일브랜디 일산킨텍스점</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>츠키네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>minvl@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1325-6774</t>
+          <t>0507-1328-9708</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_b_randy</t>
+          <t>https://www.instagram.com/thuki_nail/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5473,13 +5497,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="Q54" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,17 +5512,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1125128328</t>
+          <t>1363998342</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125128328</t>
+          <t>https://m.place.naver.com/place/1363998342</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5510,39 +5534,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일오티디</t>
+          <t>네일스튜디오하몽</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yoorrimchang@naver.com</t>
+          <t>laviedekey@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1429-0763</t>
+          <t>0507-1480-0355</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 184 우신프라자 1층 117호</t>
+          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 111호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_yxaxcxiK/chat</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5558,22 +5582,22 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>152</v>
+        <v>585</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="R55" t="n">
-        <v>161</v>
+        <v>609</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,17 +5606,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026395486</t>
+          <t>1865813904</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026395486</t>
+          <t>https://m.place.naver.com/place/1865813904</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5604,34 +5628,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>제이 뷰티 클리어</t>
+          <t>아르다뷰티 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jonghyun0823@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1342-8831</t>
+          <t>0507-1354-1704</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 311호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBf6NdCd</t>
+          <t>https://pf.kakao.com/_qJhgb</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5661,13 +5685,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>354</v>
+        <v>169</v>
       </c>
       <c r="Q56" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="R56" t="n">
-        <v>394</v>
+        <v>178</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,17 +5700,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1701276497</t>
+          <t>1958887188</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701276497</t>
+          <t>https://m.place.naver.com/place/1958887188</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5698,25 +5722,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오묘네일</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>바이마이네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jjeong_1004_@naver.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1351-1060</t>
+          <t>0507-1303-0274</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1130 상가동 제비1층 12호</t>
+          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/5.myo_art</t>
+          <t>https://www.instagram.com/bymynail_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5751,13 +5779,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="R57" t="n">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5794,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1036508811</t>
+          <t>1712300996</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036508811</t>
+          <t>https://m.place.naver.com/place/1712300996</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5788,29 +5816,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일바이아르</t>
+          <t>네일브랜디 일산킨텍스점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>nailbyare@naver.com</t>
+          <t>lunefronde@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1441-7961</t>
+          <t>0507-1325-6774</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 55-8 1층 네일바이아르</t>
+          <t>경기도 고양시 일산서구 킨텍스로 255 일산디엠시티 상가 105동 2층 243호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyare/</t>
+          <t>https://www.instagram.com/nail_b_randy</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5845,13 +5873,13 @@
         </is>
       </c>
       <c r="P58" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q58" t="n">
         <v>64</v>
       </c>
-      <c r="Q58" t="n">
-        <v>5</v>
-      </c>
       <c r="R58" t="n">
-        <v>69</v>
+        <v>328</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5888,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2094840936</t>
+          <t>1125128328</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094840936</t>
+          <t>https://m.place.naver.com/place/1125128328</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5882,25 +5910,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일르엘</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>네일디어원</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>eee2sia@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1371-6033</t>
+          <t>0507-1417-4781</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 203호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 E동 127-1호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaLFXG/chat</t>
+          <t>https://pf.kakao.com/_xlCxgxbG</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5935,13 +5967,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>309</v>
+        <v>904</v>
       </c>
       <c r="Q59" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="R59" t="n">
-        <v>360</v>
+        <v>975</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,17 +5982,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1006093671</t>
+          <t>1054380281</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006093671</t>
+          <t>https://m.place.naver.com/place/1054380281</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5972,29 +6004,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일앤스타일</t>
+          <t>주디네일 정발산본점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>nailnstyle_@naver.com</t>
+          <t>rkflrkfl1@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1438-5770</t>
+          <t>0507-1464-0970</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 253호</t>
+          <t>경기도 고양시 일산동구 일산로380번길 25-5 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nstyle_lab</t>
+          <t>https://blog.naver.com/rkflrkfl1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6009,7 +6041,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6029,13 +6061,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3038</v>
+        <v>444</v>
       </c>
       <c r="Q60" t="n">
-        <v>830</v>
+        <v>21</v>
       </c>
       <c r="R60" t="n">
-        <v>3868</v>
+        <v>465</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,17 +6076,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>31424432</t>
+          <t>1885034449</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31424432</t>
+          <t>https://m.place.naver.com/place/1885034449</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6066,25 +6098,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일,숩</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>무이네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>baeyou0417@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1325-8243</t>
+          <t>0507-1351-6051</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강선로 70 gs 프레쉬 2층 상가 201호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-17 트루엘파크스테이 212호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___soop</t>
+          <t>https://www.instagram.com/muinail_</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6119,13 +6155,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R61" t="n">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,17 +6170,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1126898433</t>
+          <t>1218582286</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126898433</t>
+          <t>https://m.place.naver.com/place/1218582286</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6156,29 +6192,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>별빛네일</t>
+          <t>라온네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>naminail@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1311-0283</t>
+          <t>0507-1463-2316</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 1층 104호</t>
+          <t>경기도 고양시 일산동구 강석로 33 상가동 105호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_byeolbit_nail/</t>
+          <t>https://www.instagram.com/rao_nnail?igshid=OGQ5ZDc2ODk2ZA==</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6204,7 +6240,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6213,13 +6249,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>252</v>
+        <v>554</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>137</v>
       </c>
       <c r="R62" t="n">
-        <v>263</v>
+        <v>691</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6228,17 +6264,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2011766876</t>
+          <t>1105591278</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011766876</t>
+          <t>https://m.place.naver.com/place/1105591278</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6250,29 +6286,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>다다네일</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tykd2048@naver.com</t>
+          <t>youngnail0121@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1418-7723</t>
+          <t>0507-1411-7300</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 15 드림월드빌딩 208호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운 1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dada._.nail/</t>
+          <t>https://www.instagram.com/youngnail0121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6307,13 +6343,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>81</v>
+        <v>789</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="R63" t="n">
-        <v>103</v>
+        <v>1076</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6322,17 +6358,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1226786349</t>
+          <t>13464862</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226786349</t>
+          <t>https://m.place.naver.com/place/13464862</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6344,25 +6380,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일맑음래쉬</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>아토네일스튜디오 일산</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sesehhh@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1356-7749</t>
+          <t>0507-1461-2141</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 379호</t>
+          <t>경기도 고양시 일산동구 중앙로 1055 레이크하임 2층 208호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.malgeum__official?igsh=MXNudWsxbXZvYjF6NA%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6372,7 +6412,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6393,17 +6433,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>37</v>
+        <v>929</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>543</v>
       </c>
       <c r="R64" t="n">
-        <v>46</v>
+        <v>1472</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,17 +6452,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1604742986</t>
+          <t>1419778439</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604742986</t>
+          <t>https://m.place.naver.com/place/1419778439</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6434,29 +6474,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>츠키네일</t>
+          <t>발톱닥터</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>minvl@naver.com</t>
+          <t>jallana@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1328-9708</t>
+          <t>0507-1409-8838</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-7 메리트윈 5층 503-a 츠키네일</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 11 근생 1동 203호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thuki_nail/</t>
+          <t>https://www.instagram.com/bt_doctor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6491,13 +6531,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>343</v>
+        <v>155</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="R65" t="n">
-        <v>345</v>
+        <v>479</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,17 +6546,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1363998342</t>
+          <t>36651631</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363998342</t>
+          <t>https://m.place.naver.com/place/36651631</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6528,29 +6568,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일무아</t>
+          <t>제이 뷰티 클리어</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>loowowool@naver.com</t>
+          <t>jonghyun0823@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1322-4700</t>
+          <t>0507-1342-8831</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 255 2층 237호</t>
+          <t>경기도 고양시 일산동구 강석로 5 1동 5층 502호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mua_</t>
+          <t>https://open.kakao.com/o/sBf6NdCd</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6576,7 +6616,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6585,13 +6625,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>92</v>
+        <v>354</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R66" t="n">
-        <v>92</v>
+        <v>394</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6600,17 +6640,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2028306533</t>
+          <t>1701276497</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028306533</t>
+          <t>https://m.place.naver.com/place/1701276497</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6622,29 +6662,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일팩토리</t>
+          <t>네일더우디</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nailfactory13@naver.com</t>
+          <t>hwyoo92@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1323-3381</t>
+          <t>0507-1358-7156</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 2층 219호</t>
+          <t>경기도 고양시 일산서구 중앙로 1470 동부썬프라자 2층 3동 203호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https:///linktr.ee/Nail_Factory13</t>
+          <t>https://www.instagram.com/nail_thewoody</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6670,7 +6710,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6679,13 +6719,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1023</v>
+        <v>326</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="R67" t="n">
-        <v>1033</v>
+        <v>408</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6694,17 +6734,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1383137709</t>
+          <t>1243502592</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383137709</t>
+          <t>https://m.place.naver.com/place/1243502592</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6716,29 +6756,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>레푸스 일산장항점</t>
+          <t>렐라네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>yoonaejang@naver.com</t>
+          <t>cinderellais@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1395-4179</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 제아이 A동 2층 202호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-34 라페스타 C동 206호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCi9vEmR9f59J8rbwKvkjlMw</t>
+          <t>https://www.instagram.com/rella_nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6753,7 +6789,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6764,22 +6800,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1922</v>
+        <v>4</v>
       </c>
       <c r="Q68" t="n">
-        <v>645</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>2567</v>
+        <v>7</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6788,17 +6824,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>90030989</t>
+          <t>1949626855</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/90030989</t>
+          <t>https://m.place.naver.com/place/1949626855</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6810,29 +6846,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>기린네일</t>
+          <t>네일 바이 무제</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ssso131@naver.com</t>
+          <t>su28min5054@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1468-7932</t>
+          <t>0507-1330-5463</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 상가동 5층 에스11호</t>
+          <t>경기도 고양시 일산동구 일산로135번길 14-6 1층 네일바이무제</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kirrin_nail</t>
+          <t>https://www.instagram.com/nails_by_mooze</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6867,13 +6903,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="Q69" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="R69" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6882,17 +6918,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1349667462</t>
+          <t>1593406269</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349667462</t>
+          <t>https://m.place.naver.com/place/1593406269</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6904,29 +6940,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>바이마이네일</t>
+          <t>네일뮤토</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jjeong_1004_@naver.com</t>
+          <t>ithgml123@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1303-0274</t>
+          <t>0507-1370-0857</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백석로71번길 14-3 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1011 현대밀라트 2차 A동 1층 102호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymynail_</t>
+          <t>https://www.instagram.com/nail_muto/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6961,13 +6997,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
         <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>196</v>
+        <v>15</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,17 +7012,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1712300996</t>
+          <t>1260058171</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712300996</t>
+          <t>https://m.place.naver.com/place/1260058171</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6998,34 +7034,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S뷰티네일 일산주엽점</t>
+          <t>네일리쉬</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>s-beauty06@naver.com</t>
+          <t>moonnsleep@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1327-9513</t>
+          <t>0507-1384-3764</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 2층 213호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 3층 312호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s-beauty06</t>
+          <t>http://pf.kakao.com/_CRNHxd</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7035,7 +7071,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7046,22 +7082,22 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>478</v>
+        <v>242</v>
       </c>
       <c r="Q71" t="n">
-        <v>426</v>
+        <v>30</v>
       </c>
       <c r="R71" t="n">
-        <v>904</v>
+        <v>272</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7070,17 +7106,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1247940545</t>
+          <t>1946279327</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247940545</t>
+          <t>https://m.place.naver.com/place/1946279327</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7092,29 +7128,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>소울메이트네일샵</t>
+          <t>네일 드 제니</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>algmlspdlf@naver.com</t>
+          <t>hja1213@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1382-5531</t>
+          <t>0507-1416-4932</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 223호</t>
+          <t>경기도 고양시 일산서구 탄현로 60 탄현7단지 상가동 117호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/soulmatenail</t>
+          <t>https://www.instagram.com/nail_de_jeny</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7140,7 +7176,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7149,13 +7185,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>229</v>
+        <v>154</v>
       </c>
       <c r="Q72" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>392</v>
+        <v>155</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,17 +7200,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>36620432</t>
+          <t>1635177150</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36620432</t>
+          <t>https://m.place.naver.com/place/1635177150</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7186,25 +7222,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>뮤다네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>페디힐 일산주엽점 내성발톱&amp;무좀발톱&amp;발각질 관리</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jujunail0713@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1389-7130</t>
+          <t>0507-1404-4143</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 5 화이트스톤 218호</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아빌딩 409호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/myuda_nail/</t>
+          <t>https://www.instagram.com/pediheal_ilsan</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7239,13 +7279,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="Q73" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="R73" t="n">
-        <v>290</v>
+        <v>486</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,17 +7294,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1129578077</t>
+          <t>13092675</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129578077</t>
+          <t>https://m.place.naver.com/place/13092675</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7276,30 +7316,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>포쉬네일 홈플러스킨텍스점</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>비온네일 일산킨텍스점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>feb_7th@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1333-4281</t>
+          <t>0507-1384-4180</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 홈플러스킨텍스점 B1층</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 상가동 지하1층 152호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/forsynail_kintex</t>
+          <t>http://pf.kakao.com/_HDxnPn</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7320,7 +7364,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7329,13 +7373,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="Q74" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="R74" t="n">
-        <v>532</v>
+        <v>114</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,17 +7388,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1485591782</t>
+          <t>1988141515</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485591782</t>
+          <t>https://m.place.naver.com/place/1988141515</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7366,29 +7410,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일은뷰티</t>
+          <t>그리심네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>topnailjina@naver.com</t>
+          <t>herb2592@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1393-0807</t>
+          <t>0507-1329-7483</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로463번길 15-13 1층</t>
+          <t>경기도 고양시 일산서구 고양대로 666 상가동 2층 D211호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_eunbeauty</t>
+          <t>https://blog.naver.com/herb2592</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7403,7 +7447,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7423,13 +7467,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>445</v>
+        <v>257</v>
       </c>
       <c r="Q75" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="R75" t="n">
-        <v>549</v>
+        <v>349</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7482,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1421368108</t>
+          <t>1667004401</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421368108</t>
+          <t>https://m.place.naver.com/place/1667004401</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7460,25 +7504,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>마이유네일</t>
+          <t>레몬네일 풍동점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>tasha81@naver.com</t>
+          <t>jamsso_couple@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1311-3135</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로430번길 74-11 1층 마이유네일 (도로변쪽 입구)</t>
+          <t>경기도 고양시 일산동구 숲속마을1로 29-37 서광미르프라자 102호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/my_u_nail</t>
+          <t>http://www.instagram.com/lemonshop_diary</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7513,13 +7561,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>63</v>
+        <v>594</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>65</v>
+        <v>598</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7528,17 +7576,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2037646051</t>
+          <t>1457328873</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037646051</t>
+          <t>https://m.place.naver.com/place/1457328873</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
